--- a/data/trans_orig/P2A_psíq_R-Edad-trans_orig.xlsx
+++ b/data/trans_orig/P2A_psíq_R-Edad-trans_orig.xlsx
@@ -538,7 +538,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Hogares según si tienen personas con limitación por discapacidad psíquica en 2007</t>
+          <t>Hogares según si tienen personas con limitación por discapacidad psíquica en 2007 (tasa de respuesta: 100,0%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -733,97 +733,97 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G4" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="H4" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="I4" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="J4" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K4" s="2" t="inlineStr">
+        <is>
+          <t>983</t>
+        </is>
+      </c>
+      <c r="L4" s="2" t="inlineStr">
+        <is>
           <t>0</t>
         </is>
       </c>
-      <c r="F4" s="2" t="inlineStr">
-        <is>
-          <t>1897</t>
-        </is>
-      </c>
-      <c r="G4" s="2" t="inlineStr">
+      <c r="M4" s="2" t="inlineStr">
+        <is>
+          <t>4917</t>
+        </is>
+      </c>
+      <c r="N4" s="2" t="inlineStr">
+        <is>
+          <t>0,21%</t>
+        </is>
+      </c>
+      <c r="O4" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="H4" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
-        </is>
-      </c>
-      <c r="I4" s="2" t="inlineStr">
-        <is>
-          <t>0,38%</t>
-        </is>
-      </c>
-      <c r="J4" s="2" t="inlineStr">
+      <c r="P4" s="2" t="inlineStr">
+        <is>
+          <t>1,05%</t>
+        </is>
+      </c>
+      <c r="Q4" s="2" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="K4" s="2" t="inlineStr">
+      <c r="R4" s="2" t="inlineStr">
         <is>
           <t>983</t>
         </is>
       </c>
-      <c r="L4" s="2" t="inlineStr">
+      <c r="S4" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="M4" s="2" t="inlineStr">
-        <is>
-          <t>5542</t>
-        </is>
-      </c>
-      <c r="N4" s="2" t="inlineStr">
-        <is>
-          <t>0,21%</t>
-        </is>
-      </c>
-      <c r="O4" s="2" t="inlineStr">
+      <c r="T4" s="2" t="inlineStr">
+        <is>
+          <t>4444</t>
+        </is>
+      </c>
+      <c r="U4" s="2" t="inlineStr">
+        <is>
+          <t>0,1%</t>
+        </is>
+      </c>
+      <c r="V4" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="P4" s="2" t="inlineStr">
-        <is>
-          <t>1,19%</t>
-        </is>
-      </c>
-      <c r="Q4" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="R4" s="2" t="inlineStr">
-        <is>
-          <t>983</t>
-        </is>
-      </c>
-      <c r="S4" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="T4" s="2" t="inlineStr">
-        <is>
-          <t>5641</t>
-        </is>
-      </c>
-      <c r="U4" s="2" t="inlineStr">
-        <is>
-          <t>0,1%</t>
-        </is>
-      </c>
-      <c r="V4" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>0,59%</t>
+          <t>0,46%</t>
         </is>
       </c>
     </row>
@@ -846,12 +846,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>492167</t>
+          <t>—</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>494064</t>
+          <t>—</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -861,12 +861,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>99,62%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>100%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -881,7 +881,7 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>461947</t>
+          <t>462572</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
@@ -896,7 +896,7 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>98,81%</t>
+          <t>98,95%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
@@ -916,7 +916,7 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>955912</t>
+          <t>957109</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
@@ -931,7 +931,7 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>99,41%</t>
+          <t>99,54%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
@@ -1076,12 +1076,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>884</t>
+          <t>881</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>8090</t>
+          <t>8777</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -1096,7 +1096,7 @@
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>1,1%</t>
+          <t>1,19%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -1111,12 +1111,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>956</t>
+          <t>0</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>8017</t>
+          <t>7959</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -1126,47 +1126,47 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="P7" s="2" t="inlineStr">
+        <is>
+          <t>1,27%</t>
+        </is>
+      </c>
+      <c r="Q7" s="2" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="R7" s="2" t="inlineStr">
+        <is>
+          <t>5971</t>
+        </is>
+      </c>
+      <c r="S7" s="2" t="inlineStr">
+        <is>
+          <t>2073</t>
+        </is>
+      </c>
+      <c r="T7" s="2" t="inlineStr">
+        <is>
+          <t>12268</t>
+        </is>
+      </c>
+      <c r="U7" s="2" t="inlineStr">
+        <is>
+          <t>0,44%</t>
+        </is>
+      </c>
+      <c r="V7" s="2" t="inlineStr">
+        <is>
           <t>0,15%</t>
         </is>
       </c>
-      <c r="P7" s="2" t="inlineStr">
-        <is>
-          <t>1,28%</t>
-        </is>
-      </c>
-      <c r="Q7" s="2" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
-      <c r="R7" s="2" t="inlineStr">
-        <is>
-          <t>5971</t>
-        </is>
-      </c>
-      <c r="S7" s="2" t="inlineStr">
-        <is>
-          <t>1993</t>
-        </is>
-      </c>
-      <c r="T7" s="2" t="inlineStr">
-        <is>
-          <t>11503</t>
-        </is>
-      </c>
-      <c r="U7" s="2" t="inlineStr">
-        <is>
-          <t>0,44%</t>
-        </is>
-      </c>
-      <c r="V7" s="2" t="inlineStr">
-        <is>
-          <t>0,15%</t>
-        </is>
-      </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>0,85%</t>
+          <t>0,9%</t>
         </is>
       </c>
     </row>
@@ -1189,12 +1189,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>727399</t>
+          <t>726712</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>734605</t>
+          <t>734608</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -1204,7 +1204,7 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>98,9%</t>
+          <t>98,81%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
@@ -1224,12 +1224,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>617477</t>
+          <t>617535</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>624538</t>
+          <t>625494</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -1239,12 +1239,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>98,72%</t>
+          <t>98,73%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>99,85%</t>
+          <t>100,0%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1259,12 +1259,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>1349479</t>
+          <t>1348714</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>1358989</t>
+          <t>1358909</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -1274,7 +1274,7 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>99,15%</t>
+          <t>99,1%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
@@ -1419,12 +1419,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>1616</t>
+          <t>1583</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>13350</t>
+          <t>13807</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1439,7 +1439,7 @@
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>2,09%</t>
+          <t>2,16%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1454,12 +1454,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>3096</t>
+          <t>3136</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>14898</t>
+          <t>14602</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -1474,7 +1474,7 @@
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>2,16%</t>
+          <t>2,12%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1489,12 +1489,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>6828</t>
+          <t>7252</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>22922</t>
+          <t>22967</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -1504,7 +1504,7 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>0,51%</t>
+          <t>0,55%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
@@ -1532,12 +1532,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>625318</t>
+          <t>624861</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>637052</t>
+          <t>637085</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -1547,7 +1547,7 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>97,91%</t>
+          <t>97,84%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
@@ -1567,12 +1567,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>674846</t>
+          <t>675142</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>686648</t>
+          <t>686608</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -1582,7 +1582,7 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>97,84%</t>
+          <t>97,88%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
@@ -1602,12 +1602,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>1305490</t>
+          <t>1305445</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>1321584</t>
+          <t>1321160</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -1622,7 +1622,7 @@
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>99,49%</t>
+          <t>99,45%</t>
         </is>
       </c>
     </row>
@@ -1762,12 +1762,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>4137</t>
+          <t>4158</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>16792</t>
+          <t>16619</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -1782,7 +1782,7 @@
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>3,23%</t>
+          <t>3,2%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -1797,12 +1797,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>4904</t>
+          <t>5009</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>17055</t>
+          <t>17748</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -1812,12 +1812,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>0,95%</t>
+          <t>0,97%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>3,31%</t>
+          <t>3,44%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1832,12 +1832,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>11504</t>
+          <t>10675</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>29757</t>
+          <t>28824</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -1847,12 +1847,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>1,11%</t>
+          <t>1,03%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>2,88%</t>
+          <t>2,79%</t>
         </is>
       </c>
     </row>
@@ -1875,12 +1875,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>502355</t>
+          <t>502528</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>515010</t>
+          <t>514989</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1890,7 +1890,7 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>96,77%</t>
+          <t>96,8%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
@@ -1910,12 +1910,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>498587</t>
+          <t>497894</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>510738</t>
+          <t>510633</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -1925,12 +1925,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>96,69%</t>
+          <t>96,56%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>99,05%</t>
+          <t>99,03%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1945,12 +1945,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>1005032</t>
+          <t>1005965</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>1023285</t>
+          <t>1024114</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -1960,12 +1960,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>97,12%</t>
+          <t>97,21%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>98,89%</t>
+          <t>98,97%</t>
         </is>
       </c>
     </row>
@@ -2110,7 +2110,7 @@
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>6102</t>
+          <t>6163</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -2125,7 +2125,7 @@
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>1,58%</t>
+          <t>1,59%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -2140,12 +2140,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>2216</t>
+          <t>2931</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>12809</t>
+          <t>14863</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -2155,12 +2155,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>0,55%</t>
+          <t>0,73%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>3,17%</t>
+          <t>3,68%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2175,12 +2175,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>3893</t>
+          <t>3960</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>15860</t>
+          <t>16326</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -2190,12 +2190,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>0,49%</t>
+          <t>0,5%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>2,01%</t>
+          <t>2,06%</t>
         </is>
       </c>
     </row>
@@ -2218,7 +2218,7 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>380608</t>
+          <t>380547</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
@@ -2233,7 +2233,7 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>98,42%</t>
+          <t>98,41%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
@@ -2253,12 +2253,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>391177</t>
+          <t>389123</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>401770</t>
+          <t>401055</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -2268,12 +2268,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>96,83%</t>
+          <t>96,32%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>99,45%</t>
+          <t>99,27%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2288,12 +2288,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>774836</t>
+          <t>774370</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>786803</t>
+          <t>786736</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -2303,12 +2303,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>97,99%</t>
+          <t>97,94%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>99,51%</t>
+          <t>99,5%</t>
         </is>
       </c>
     </row>
@@ -2448,12 +2448,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>943</t>
+          <t>935</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>8144</t>
+          <t>9168</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -2468,7 +2468,7 @@
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>2,78%</t>
+          <t>3,13%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -2483,12 +2483,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>1799</t>
+          <t>1794</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>10251</t>
+          <t>10041</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -2503,7 +2503,7 @@
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>2,99%</t>
+          <t>2,93%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -2518,12 +2518,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>3712</t>
+          <t>4465</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>14709</t>
+          <t>15603</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -2533,12 +2533,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>0,58%</t>
+          <t>0,7%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>2,31%</t>
+          <t>2,46%</t>
         </is>
       </c>
     </row>
@@ -2561,12 +2561,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>284439</t>
+          <t>283415</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>291640</t>
+          <t>291648</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -2576,7 +2576,7 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>97,22%</t>
+          <t>96,87%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
@@ -2596,12 +2596,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>332683</t>
+          <t>332893</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>341135</t>
+          <t>341140</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -2611,7 +2611,7 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>97,01%</t>
+          <t>97,07%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
@@ -2631,12 +2631,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>620808</t>
+          <t>619914</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>631805</t>
+          <t>631052</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -2646,12 +2646,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>97,69%</t>
+          <t>97,54%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>99,42%</t>
+          <t>99,3%</t>
         </is>
       </c>
     </row>
@@ -2791,12 +2791,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>2570</t>
+          <t>2742</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>14345</t>
+          <t>14738</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -2806,12 +2806,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>1,22%</t>
+          <t>1,31%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>6,83%</t>
+          <t>7,02%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -2826,12 +2826,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>2716</t>
+          <t>3254</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>15312</t>
+          <t>15300</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -2841,12 +2841,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>0,81%</t>
+          <t>0,97%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>4,59%</t>
+          <t>4,58%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -2861,12 +2861,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>8181</t>
+          <t>8097</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>23612</t>
+          <t>24597</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -2876,12 +2876,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>1,5%</t>
+          <t>1,49%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>4,34%</t>
+          <t>4,52%</t>
         </is>
       </c>
     </row>
@@ -2904,12 +2904,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>195538</t>
+          <t>195145</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>207313</t>
+          <t>207141</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -2919,12 +2919,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>93,17%</t>
+          <t>92,98%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>98,78%</t>
+          <t>98,69%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -2939,12 +2939,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>318596</t>
+          <t>318608</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>331192</t>
+          <t>330654</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -2954,12 +2954,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>95,41%</t>
+          <t>95,42%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>99,19%</t>
+          <t>99,03%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -2974,12 +2974,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>520179</t>
+          <t>519194</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>535610</t>
+          <t>535694</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -2989,12 +2989,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>95,66%</t>
+          <t>95,48%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>98,5%</t>
+          <t>98,51%</t>
         </is>
       </c>
     </row>
@@ -3134,12 +3134,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>19763</t>
+          <t>20150</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>41995</t>
+          <t>42995</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -3149,12 +3149,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>0,6%</t>
+          <t>0,61%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>1,28%</t>
+          <t>1,31%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -3169,12 +3169,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>28622</t>
+          <t>28386</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>53787</t>
+          <t>53962</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -3184,12 +3184,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>0,85%</t>
+          <t>0,84%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>1,59%</t>
+          <t>1,6%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -3204,12 +3204,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>53688</t>
+          <t>54557</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>87187</t>
+          <t>87362</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -3219,7 +3219,7 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>0,81%</t>
+          <t>0,82%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
@@ -3247,12 +3247,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>3234548</t>
+          <t>3233548</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>3256780</t>
+          <t>3256393</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -3262,12 +3262,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>98,72%</t>
+          <t>98,69%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>99,4%</t>
+          <t>99,39%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -3282,12 +3282,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>3325410</t>
+          <t>3325235</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>3350575</t>
+          <t>3350811</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -3297,12 +3297,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>98,41%</t>
+          <t>98,4%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>99,15%</t>
+          <t>99,16%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -3317,12 +3317,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>6568554</t>
+          <t>6568379</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>6602053</t>
+          <t>6601184</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -3337,7 +3337,7 @@
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>99,19%</t>
+          <t>99,18%</t>
         </is>
       </c>
     </row>
@@ -3517,7 +3517,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Hogares según si tienen personas con limitación por discapacidad psíquica en 2012</t>
+          <t>Hogares según si tienen personas con limitación por discapacidad psíquica en 2012 (tasa de respuesta: 100,0%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -3712,12 +3712,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>931</t>
+          <t>937</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>8279</t>
+          <t>7730</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -3732,7 +3732,7 @@
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>1,82%</t>
+          <t>1,7%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -3747,12 +3747,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>3707</t>
+          <t>3808</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>14351</t>
+          <t>15117</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -3762,12 +3762,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>0,86%</t>
+          <t>0,89%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>3,34%</t>
+          <t>3,51%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -3782,12 +3782,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>5728</t>
+          <t>5716</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>17857</t>
+          <t>17606</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -3802,7 +3802,7 @@
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>2,02%</t>
+          <t>1,99%</t>
         </is>
       </c>
     </row>
@@ -3825,12 +3825,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>445867</t>
+          <t>446416</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>453215</t>
+          <t>453209</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -3840,7 +3840,7 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>98,18%</t>
+          <t>98,3%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
@@ -3860,12 +3860,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>415879</t>
+          <t>415113</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>426523</t>
+          <t>426422</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -3875,12 +3875,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>96,66%</t>
+          <t>96,49%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>99,14%</t>
+          <t>99,11%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -3895,12 +3895,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>866519</t>
+          <t>866770</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>878648</t>
+          <t>878660</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -3910,7 +3910,7 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>97,98%</t>
+          <t>98,01%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
@@ -4055,12 +4055,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>5027</t>
+          <t>4703</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>19325</t>
+          <t>19566</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -4070,12 +4070,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>0,73%</t>
+          <t>0,68%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>2,81%</t>
+          <t>2,85%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -4090,12 +4090,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>1888</t>
+          <t>1912</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>12784</t>
+          <t>13173</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -4110,7 +4110,7 @@
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>2,09%</t>
+          <t>2,16%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -4125,12 +4125,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>9481</t>
+          <t>8913</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>28089</t>
+          <t>25886</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -4140,12 +4140,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>0,73%</t>
+          <t>0,69%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>2,17%</t>
+          <t>2,0%</t>
         </is>
       </c>
     </row>
@@ -4168,12 +4168,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>667762</t>
+          <t>667521</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>682060</t>
+          <t>682384</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -4183,12 +4183,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>97,19%</t>
+          <t>97,15%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>99,27%</t>
+          <t>99,32%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -4203,12 +4203,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>597471</t>
+          <t>597082</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>608367</t>
+          <t>608343</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -4218,7 +4218,7 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>97,91%</t>
+          <t>97,84%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
@@ -4238,12 +4238,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>1269253</t>
+          <t>1271456</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>1287861</t>
+          <t>1288429</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -4253,12 +4253,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>97,83%</t>
+          <t>98,0%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>99,27%</t>
+          <t>99,31%</t>
         </is>
       </c>
     </row>
@@ -4398,12 +4398,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>3881</t>
+          <t>3787</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>18352</t>
+          <t>17547</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -4413,12 +4413,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>0,57%</t>
+          <t>0,56%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>2,69%</t>
+          <t>2,57%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -4433,12 +4433,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>13554</t>
+          <t>14072</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>32785</t>
+          <t>34198</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -4448,12 +4448,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>1,91%</t>
+          <t>1,98%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>4,61%</t>
+          <t>4,81%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -4468,12 +4468,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>19957</t>
+          <t>19826</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>43953</t>
+          <t>43789</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -4483,12 +4483,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>1,43%</t>
+          <t>1,42%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>3,16%</t>
+          <t>3,14%</t>
         </is>
       </c>
     </row>
@@ -4511,12 +4511,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>663511</t>
+          <t>664316</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>677982</t>
+          <t>678076</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -4526,12 +4526,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>97,31%</t>
+          <t>97,43%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>99,43%</t>
+          <t>99,44%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -4546,12 +4546,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>678065</t>
+          <t>676652</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>697296</t>
+          <t>696778</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -4561,12 +4561,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>95,39%</t>
+          <t>95,19%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>98,09%</t>
+          <t>98,02%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -4581,12 +4581,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>1348759</t>
+          <t>1348923</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>1372755</t>
+          <t>1372886</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -4596,12 +4596,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>96,84%</t>
+          <t>96,86%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>98,57%</t>
+          <t>98,58%</t>
         </is>
       </c>
     </row>
@@ -4741,12 +4741,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>6483</t>
+          <t>6377</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>24269</t>
+          <t>23502</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -4756,12 +4756,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>1,05%</t>
+          <t>1,04%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>3,95%</t>
+          <t>3,82%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -4776,12 +4776,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>8969</t>
+          <t>8436</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>24813</t>
+          <t>24584</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -4791,12 +4791,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>1,46%</t>
+          <t>1,37%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>4,03%</t>
+          <t>3,99%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -4811,12 +4811,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>18189</t>
+          <t>19680</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>41902</t>
+          <t>40472</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -4826,12 +4826,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>1,48%</t>
+          <t>1,6%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>3,4%</t>
+          <t>3,29%</t>
         </is>
       </c>
     </row>
@@ -4854,12 +4854,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>590348</t>
+          <t>591115</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>608134</t>
+          <t>608240</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -4869,12 +4869,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>96,05%</t>
+          <t>96,18%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>98,95%</t>
+          <t>98,96%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -4889,12 +4889,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>591386</t>
+          <t>591615</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>607230</t>
+          <t>607763</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -4904,12 +4904,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>95,97%</t>
+          <t>96,01%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>98,54%</t>
+          <t>98,63%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -4924,12 +4924,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>1188914</t>
+          <t>1190344</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>1212627</t>
+          <t>1211136</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -4939,12 +4939,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>96,6%</t>
+          <t>96,71%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>98,52%</t>
+          <t>98,4%</t>
         </is>
       </c>
     </row>
@@ -5084,12 +5084,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>5224</t>
+          <t>5784</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>18638</t>
+          <t>20982</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -5099,12 +5099,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>1,22%</t>
+          <t>1,35%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>4,34%</t>
+          <t>4,89%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -5119,12 +5119,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>4256</t>
+          <t>4983</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>17837</t>
+          <t>18411</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -5134,12 +5134,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>0,95%</t>
+          <t>1,11%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>3,98%</t>
+          <t>4,11%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -5154,12 +5154,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>13112</t>
+          <t>12105</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>31451</t>
+          <t>31361</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -5169,12 +5169,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>1,49%</t>
+          <t>1,38%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>3,59%</t>
+          <t>3,58%</t>
         </is>
       </c>
     </row>
@@ -5197,12 +5197,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>410791</t>
+          <t>408447</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>424205</t>
+          <t>423645</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -5212,12 +5212,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>95,66%</t>
+          <t>95,11%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>98,78%</t>
+          <t>98,65%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -5232,12 +5232,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>429963</t>
+          <t>429389</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>443544</t>
+          <t>442817</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -5247,12 +5247,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>96,02%</t>
+          <t>95,89%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>99,05%</t>
+          <t>98,89%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -5267,12 +5267,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>845778</t>
+          <t>845868</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>864117</t>
+          <t>865124</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -5282,12 +5282,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>96,41%</t>
+          <t>96,42%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>98,51%</t>
+          <t>98,62%</t>
         </is>
       </c>
     </row>
@@ -5427,12 +5427,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>4761</t>
+          <t>4849</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>18437</t>
+          <t>18766</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -5442,12 +5442,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>1,54%</t>
+          <t>1,57%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>5,95%</t>
+          <t>6,06%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -5462,12 +5462,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>977</t>
+          <t>970</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>10998</t>
+          <t>11659</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -5477,12 +5477,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>0,28%</t>
+          <t>0,27%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>3,11%</t>
+          <t>3,29%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -5497,12 +5497,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>7093</t>
+          <t>6843</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>21969</t>
+          <t>23016</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -5512,12 +5512,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>1,07%</t>
+          <t>1,03%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>3,31%</t>
+          <t>3,47%</t>
         </is>
       </c>
     </row>
@@ -5540,12 +5540,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>291349</t>
+          <t>291020</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>305025</t>
+          <t>304937</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -5555,12 +5555,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>94,05%</t>
+          <t>93,94%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>98,46%</t>
+          <t>98,43%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -5575,12 +5575,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>342998</t>
+          <t>342337</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>353019</t>
+          <t>353026</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -5590,12 +5590,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>96,89%</t>
+          <t>96,71%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>99,72%</t>
+          <t>99,73%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -5610,12 +5610,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>641813</t>
+          <t>640766</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>656689</t>
+          <t>656939</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -5625,12 +5625,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>96,69%</t>
+          <t>96,53%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>98,93%</t>
+          <t>98,97%</t>
         </is>
       </c>
     </row>
@@ -5770,12 +5770,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>3337</t>
+          <t>3246</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>17206</t>
+          <t>17627</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -5785,12 +5785,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>1,34%</t>
+          <t>1,3%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>6,89%</t>
+          <t>7,05%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -5805,12 +5805,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>4387</t>
+          <t>4363</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>16991</t>
+          <t>17464</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -5820,12 +5820,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>1,13%</t>
+          <t>1,12%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>4,37%</t>
+          <t>4,49%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -5840,12 +5840,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>10394</t>
+          <t>10614</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>29221</t>
+          <t>28962</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -5855,12 +5855,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>1,63%</t>
+          <t>1,66%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>4,57%</t>
+          <t>4,53%</t>
         </is>
       </c>
     </row>
@@ -5883,12 +5883,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>232645</t>
+          <t>232224</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>246514</t>
+          <t>246605</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -5898,12 +5898,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>93,11%</t>
+          <t>92,95%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>98,66%</t>
+          <t>98,7%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -5918,12 +5918,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>371988</t>
+          <t>371515</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>384592</t>
+          <t>384616</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -5933,12 +5933,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>95,63%</t>
+          <t>95,51%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>98,87%</t>
+          <t>98,88%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -5953,12 +5953,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>609609</t>
+          <t>609868</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>628436</t>
+          <t>628216</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -5968,12 +5968,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>95,43%</t>
+          <t>95,47%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>98,37%</t>
+          <t>98,34%</t>
         </is>
       </c>
     </row>
@@ -6113,12 +6113,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>46068</t>
+          <t>48781</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>81624</t>
+          <t>85110</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -6128,12 +6128,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>1,34%</t>
+          <t>1,42%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>2,38%</t>
+          <t>2,48%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -6148,12 +6148,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>58274</t>
+          <t>59306</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>95142</t>
+          <t>92986</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -6163,12 +6163,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>1,64%</t>
+          <t>1,67%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>2,67%</t>
+          <t>2,61%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -6183,12 +6183,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>113673</t>
+          <t>114140</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>164089</t>
+          <t>162553</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -6203,7 +6203,7 @@
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>2,35%</t>
+          <t>2,33%</t>
         </is>
       </c>
     </row>
@@ -6226,12 +6226,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>3345155</t>
+          <t>3341669</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>3380711</t>
+          <t>3377998</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -6241,12 +6241,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>97,62%</t>
+          <t>97,52%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>98,66%</t>
+          <t>98,58%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -6261,12 +6261,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>3463167</t>
+          <t>3465323</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>3500035</t>
+          <t>3499003</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -6276,12 +6276,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>97,33%</t>
+          <t>97,39%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>98,36%</t>
+          <t>98,33%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -6296,12 +6296,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>6820999</t>
+          <t>6822535</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>6871415</t>
+          <t>6870948</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -6311,7 +6311,7 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>97,65%</t>
+          <t>97,67%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
@@ -6496,7 +6496,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Hogares según si tienen personas con limitación por discapacidad psíquica en 2016</t>
+          <t>Hogares según si tienen personas con limitación por discapacidad psíquica en 2016 (tasa de respuesta: 100,0%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -6696,7 +6696,7 @@
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>8262</t>
+          <t>9446</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -6711,7 +6711,7 @@
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>1,97%</t>
+          <t>2,25%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -6731,7 +6731,7 @@
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>6439</t>
+          <t>6364</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -6746,7 +6746,7 @@
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>1,63%</t>
+          <t>1,61%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -6761,12 +6761,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>1086</t>
+          <t>1396</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>11600</t>
+          <t>11689</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -6776,12 +6776,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>0,13%</t>
+          <t>0,17%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>1,42%</t>
+          <t>1,43%</t>
         </is>
       </c>
     </row>
@@ -6804,7 +6804,7 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>411201</t>
+          <t>410017</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
@@ -6819,7 +6819,7 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>98,03%</t>
+          <t>97,75%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
@@ -6839,7 +6839,7 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>389316</t>
+          <t>389391</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
@@ -6854,7 +6854,7 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>98,37%</t>
+          <t>98,39%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
@@ -6874,12 +6874,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>803618</t>
+          <t>803529</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>814132</t>
+          <t>813822</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -6889,12 +6889,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>98,58%</t>
+          <t>98,57%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>99,87%</t>
+          <t>99,83%</t>
         </is>
       </c>
     </row>
@@ -7034,12 +7034,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>1827</t>
+          <t>1875</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>9757</t>
+          <t>12079</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -7049,12 +7049,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>0,31%</t>
+          <t>0,32%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>1,65%</t>
+          <t>2,05%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -7069,12 +7069,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>1944</t>
+          <t>2005</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>12361</t>
+          <t>11630</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -7084,12 +7084,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>0,34%</t>
+          <t>0,36%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>2,19%</t>
+          <t>2,06%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -7104,12 +7104,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>5687</t>
+          <t>5581</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>18174</t>
+          <t>17165</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -7119,12 +7119,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>0,49%</t>
+          <t>0,48%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>1,57%</t>
+          <t>1,49%</t>
         </is>
       </c>
     </row>
@@ -7147,12 +7147,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>580739</t>
+          <t>578417</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>588669</t>
+          <t>588621</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -7162,12 +7162,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>98,35%</t>
+          <t>97,95%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>99,69%</t>
+          <t>99,68%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -7182,12 +7182,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>551183</t>
+          <t>551914</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>561600</t>
+          <t>561539</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -7197,12 +7197,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>97,81%</t>
+          <t>97,94%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>99,66%</t>
+          <t>99,64%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -7217,12 +7217,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>1135866</t>
+          <t>1136875</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>1148353</t>
+          <t>1148459</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -7232,12 +7232,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>98,43%</t>
+          <t>98,51%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>99,51%</t>
+          <t>99,52%</t>
         </is>
       </c>
     </row>
@@ -7377,12 +7377,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>891</t>
+          <t>0</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>7430</t>
+          <t>7576</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -7392,12 +7392,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>0,13%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>1,11%</t>
+          <t>1,13%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -7412,12 +7412,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>3904</t>
+          <t>4652</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>15250</t>
+          <t>16074</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -7427,12 +7427,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>0,59%</t>
+          <t>0,7%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>2,31%</t>
+          <t>2,43%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -7447,12 +7447,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>6462</t>
+          <t>6280</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>19663</t>
+          <t>19240</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -7462,12 +7462,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>0,49%</t>
+          <t>0,47%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>1,48%</t>
+          <t>1,45%</t>
         </is>
       </c>
     </row>
@@ -7490,12 +7490,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>661667</t>
+          <t>661521</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>668206</t>
+          <t>669097</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -7505,12 +7505,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>98,89%</t>
+          <t>98,87%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>99,87%</t>
+          <t>100,0%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -7525,12 +7525,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>646136</t>
+          <t>645312</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>657482</t>
+          <t>656734</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -7540,12 +7540,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>97,69%</t>
+          <t>97,57%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>99,41%</t>
+          <t>99,3%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -7560,12 +7560,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>1310820</t>
+          <t>1311243</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>1324021</t>
+          <t>1324203</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -7575,12 +7575,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>98,52%</t>
+          <t>98,55%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>99,51%</t>
+          <t>99,53%</t>
         </is>
       </c>
     </row>
@@ -7720,12 +7720,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>2815</t>
+          <t>2201</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>14573</t>
+          <t>14524</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -7735,12 +7735,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>0,44%</t>
+          <t>0,34%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>2,26%</t>
+          <t>2,25%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -7755,12 +7755,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>4475</t>
+          <t>4063</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>16757</t>
+          <t>16257</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -7770,12 +7770,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>0,69%</t>
+          <t>0,63%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>2,58%</t>
+          <t>2,5%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -7790,12 +7790,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>9457</t>
+          <t>9034</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>26375</t>
+          <t>25824</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -7805,12 +7805,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>0,73%</t>
+          <t>0,7%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>2,04%</t>
+          <t>1,99%</t>
         </is>
       </c>
     </row>
@@ -7833,12 +7833,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>631475</t>
+          <t>631524</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>643233</t>
+          <t>643847</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -7848,12 +7848,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>97,74%</t>
+          <t>97,75%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>99,56%</t>
+          <t>99,66%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -7868,12 +7868,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>632320</t>
+          <t>632820</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>644602</t>
+          <t>645014</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -7883,12 +7883,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>97,42%</t>
+          <t>97,5%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>99,31%</t>
+          <t>99,37%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -7903,12 +7903,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>1268750</t>
+          <t>1269301</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>1285668</t>
+          <t>1286091</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -7918,12 +7918,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>97,96%</t>
+          <t>98,01%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>99,27%</t>
+          <t>99,3%</t>
         </is>
       </c>
     </row>
@@ -8063,12 +8063,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>2997</t>
+          <t>3029</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>16922</t>
+          <t>15662</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -8083,7 +8083,7 @@
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>3,54%</t>
+          <t>3,28%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -8098,12 +8098,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>5535</t>
+          <t>5163</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>22488</t>
+          <t>22132</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -8113,12 +8113,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>1,11%</t>
+          <t>1,04%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>4,53%</t>
+          <t>4,45%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -8133,12 +8133,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>10780</t>
+          <t>11495</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>30849</t>
+          <t>32722</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -8148,12 +8148,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>1,11%</t>
+          <t>1,18%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>3,16%</t>
+          <t>3,36%</t>
         </is>
       </c>
     </row>
@@ -8176,12 +8176,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>460996</t>
+          <t>462256</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>474921</t>
+          <t>474889</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -8191,7 +8191,7 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>96,46%</t>
+          <t>96,72%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
@@ -8211,12 +8211,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>474361</t>
+          <t>474717</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>491314</t>
+          <t>491686</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -8226,12 +8226,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>95,47%</t>
+          <t>95,55%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>98,89%</t>
+          <t>98,96%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -8246,12 +8246,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>943918</t>
+          <t>942045</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>963987</t>
+          <t>963272</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -8261,12 +8261,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>96,84%</t>
+          <t>96,64%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>98,89%</t>
+          <t>98,82%</t>
         </is>
       </c>
     </row>
@@ -8406,12 +8406,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>2000</t>
+          <t>1928</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>11722</t>
+          <t>11754</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -8421,12 +8421,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>0,6%</t>
+          <t>0,58%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>3,51%</t>
+          <t>3,52%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -8441,12 +8441,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>4883</t>
+          <t>4696</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>17855</t>
+          <t>17729</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -8456,12 +8456,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>1,29%</t>
+          <t>1,24%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>4,73%</t>
+          <t>4,69%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -8476,12 +8476,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>8749</t>
+          <t>8825</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>25704</t>
+          <t>24857</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -8491,12 +8491,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>1,23%</t>
+          <t>1,24%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>3,61%</t>
+          <t>3,49%</t>
         </is>
       </c>
     </row>
@@ -8519,12 +8519,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>322608</t>
+          <t>322576</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>332330</t>
+          <t>332402</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -8534,12 +8534,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>96,49%</t>
+          <t>96,48%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>99,4%</t>
+          <t>99,42%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -8554,12 +8554,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>359907</t>
+          <t>360033</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>372879</t>
+          <t>373066</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -8569,12 +8569,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>95,27%</t>
+          <t>95,31%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>98,71%</t>
+          <t>98,76%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -8589,12 +8589,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>686388</t>
+          <t>687235</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>703343</t>
+          <t>703267</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -8604,12 +8604,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>96,39%</t>
+          <t>96,51%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>98,77%</t>
+          <t>98,76%</t>
         </is>
       </c>
     </row>
@@ -8754,7 +8754,7 @@
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>5753</t>
+          <t>5006</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -8769,7 +8769,7 @@
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>2,24%</t>
+          <t>1,95%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -8784,12 +8784,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>4890</t>
+          <t>4819</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>19533</t>
+          <t>19539</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -8799,7 +8799,7 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>1,22%</t>
+          <t>1,2%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
@@ -8819,12 +8819,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>6045</t>
+          <t>6184</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>20467</t>
+          <t>21556</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -8834,12 +8834,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>0,92%</t>
+          <t>0,94%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>3,11%</t>
+          <t>3,28%</t>
         </is>
       </c>
     </row>
@@ -8862,7 +8862,7 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>251245</t>
+          <t>251992</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
@@ -8877,7 +8877,7 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>97,76%</t>
+          <t>98,05%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
@@ -8897,12 +8897,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>380636</t>
+          <t>380630</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>395279</t>
+          <t>395350</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -8917,7 +8917,7 @@
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>98,78%</t>
+          <t>98,8%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -8932,12 +8932,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>636700</t>
+          <t>635611</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>651122</t>
+          <t>650983</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -8947,12 +8947,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>96,89%</t>
+          <t>96,72%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>99,08%</t>
+          <t>99,06%</t>
         </is>
       </c>
     </row>
@@ -9092,12 +9092,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>22447</t>
+          <t>21114</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>45701</t>
+          <t>46130</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -9107,12 +9107,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>0,66%</t>
+          <t>0,62%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>1,35%</t>
+          <t>1,36%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -9127,12 +9127,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>43518</t>
+          <t>42883</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>74307</t>
+          <t>74139</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -9142,12 +9142,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>1,23%</t>
+          <t>1,21%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>2,1%</t>
+          <t>2,09%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -9162,12 +9162,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>70551</t>
+          <t>71741</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>109519</t>
+          <t>113052</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -9177,12 +9177,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>1,02%</t>
+          <t>1,03%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>1,58%</t>
+          <t>1,63%</t>
         </is>
       </c>
     </row>
@@ -9205,12 +9205,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>3348649</t>
+          <t>3348220</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>3371903</t>
+          <t>3373236</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -9220,12 +9220,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>98,65%</t>
+          <t>98,64%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>99,34%</t>
+          <t>99,38%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -9240,12 +9240,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>3470235</t>
+          <t>3470403</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>3501024</t>
+          <t>3501659</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -9255,12 +9255,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>97,9%</t>
+          <t>97,91%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>98,77%</t>
+          <t>98,79%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -9275,12 +9275,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>6829373</t>
+          <t>6825840</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>6868341</t>
+          <t>6867151</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -9290,12 +9290,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>98,42%</t>
+          <t>98,37%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>98,98%</t>
+          <t>98,97%</t>
         </is>
       </c>
     </row>
@@ -9475,7 +9475,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Hogares según si tienen personas con limitación por discapacidad psíquica en 2023</t>
+          <t>Hogares según si tienen personas con limitación por discapacidad psíquica en 2023 (tasa de respuesta: 100,0%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -9670,12 +9670,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>1714</t>
+          <t>1921</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>24047</t>
+          <t>27667</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -9685,47 +9685,47 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
+          <t>0,48%</t>
+        </is>
+      </c>
+      <c r="I4" s="2" t="inlineStr">
+        <is>
+          <t>6,92%</t>
+        </is>
+      </c>
+      <c r="J4" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="K4" s="2" t="inlineStr">
+        <is>
+          <t>6092</t>
+        </is>
+      </c>
+      <c r="L4" s="2" t="inlineStr">
+        <is>
+          <t>1349</t>
+        </is>
+      </c>
+      <c r="M4" s="2" t="inlineStr">
+        <is>
+          <t>18901</t>
+        </is>
+      </c>
+      <c r="N4" s="2" t="inlineStr">
+        <is>
+          <t>1,95%</t>
+        </is>
+      </c>
+      <c r="O4" s="2" t="inlineStr">
+        <is>
           <t>0,43%</t>
         </is>
       </c>
-      <c r="I4" s="2" t="inlineStr">
-        <is>
-          <t>6,01%</t>
-        </is>
-      </c>
-      <c r="J4" s="2" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="K4" s="2" t="inlineStr">
-        <is>
-          <t>6092</t>
-        </is>
-      </c>
-      <c r="L4" s="2" t="inlineStr">
-        <is>
-          <t>1167</t>
-        </is>
-      </c>
-      <c r="M4" s="2" t="inlineStr">
-        <is>
-          <t>18246</t>
-        </is>
-      </c>
-      <c r="N4" s="2" t="inlineStr">
-        <is>
-          <t>1,95%</t>
-        </is>
-      </c>
-      <c r="O4" s="2" t="inlineStr">
-        <is>
-          <t>0,37%</t>
-        </is>
-      </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>5,83%</t>
+          <t>6,03%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -9740,12 +9740,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>5486</t>
+          <t>5482</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>32117</t>
+          <t>31147</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -9760,7 +9760,7 @@
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>4,5%</t>
+          <t>4,37%</t>
         </is>
       </c>
     </row>
@@ -9783,12 +9783,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>375940</t>
+          <t>372320</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>398273</t>
+          <t>398066</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -9798,49 +9798,49 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>93,99%</t>
+          <t>93,08%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
+          <t>99,52%</t>
+        </is>
+      </c>
+      <c r="J5" s="2" t="inlineStr">
+        <is>
+          <t>203</t>
+        </is>
+      </c>
+      <c r="K5" s="2" t="inlineStr">
+        <is>
+          <t>307108</t>
+        </is>
+      </c>
+      <c r="L5" s="2" t="inlineStr">
+        <is>
+          <t>294299</t>
+        </is>
+      </c>
+      <c r="M5" s="2" t="inlineStr">
+        <is>
+          <t>311851</t>
+        </is>
+      </c>
+      <c r="N5" s="2" t="inlineStr">
+        <is>
+          <t>98,05%</t>
+        </is>
+      </c>
+      <c r="O5" s="2" t="inlineStr">
+        <is>
+          <t>93,97%</t>
+        </is>
+      </c>
+      <c r="P5" s="2" t="inlineStr">
+        <is>
           <t>99,57%</t>
         </is>
       </c>
-      <c r="J5" s="2" t="inlineStr">
-        <is>
-          <t>203</t>
-        </is>
-      </c>
-      <c r="K5" s="2" t="inlineStr">
-        <is>
-          <t>307108</t>
-        </is>
-      </c>
-      <c r="L5" s="2" t="inlineStr">
-        <is>
-          <t>294954</t>
-        </is>
-      </c>
-      <c r="M5" s="2" t="inlineStr">
-        <is>
-          <t>312033</t>
-        </is>
-      </c>
-      <c r="N5" s="2" t="inlineStr">
-        <is>
-          <t>98,05%</t>
-        </is>
-      </c>
-      <c r="O5" s="2" t="inlineStr">
-        <is>
-          <t>94,17%</t>
-        </is>
-      </c>
-      <c r="P5" s="2" t="inlineStr">
-        <is>
-          <t>99,63%</t>
-        </is>
-      </c>
       <c r="Q5" s="2" t="inlineStr">
         <is>
           <t>370</t>
@@ -9853,12 +9853,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>681070</t>
+          <t>682040</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>707701</t>
+          <t>707705</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -9868,7 +9868,7 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>95,5%</t>
+          <t>95,63%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
@@ -10013,12 +10013,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>1080</t>
+          <t>1078</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>12401</t>
+          <t>11386</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -10028,12 +10028,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>0,26%</t>
+          <t>0,25%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>2,93%</t>
+          <t>2,69%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -10048,12 +10048,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>6501</t>
+          <t>6395</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>25160</t>
+          <t>25982</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -10063,12 +10063,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>1,27%</t>
+          <t>1,25%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>4,91%</t>
+          <t>5,07%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -10083,12 +10083,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>9423</t>
+          <t>9443</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>29664</t>
+          <t>31170</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -10103,7 +10103,7 @@
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>3,17%</t>
+          <t>3,33%</t>
         </is>
       </c>
     </row>
@@ -10126,12 +10126,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>411146</t>
+          <t>412161</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>422467</t>
+          <t>422469</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -10141,12 +10141,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>97,07%</t>
+          <t>97,31%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>99,74%</t>
+          <t>99,75%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -10161,12 +10161,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>486933</t>
+          <t>486111</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>505592</t>
+          <t>505698</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -10176,12 +10176,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>95,09%</t>
+          <t>94,93%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>98,73%</t>
+          <t>98,75%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -10196,12 +10196,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>905976</t>
+          <t>904470</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>926217</t>
+          <t>926197</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -10211,7 +10211,7 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>96,83%</t>
+          <t>96,67%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
@@ -10356,12 +10356,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>2383</t>
+          <t>2240</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>13234</t>
+          <t>13370</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -10371,12 +10371,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>0,44%</t>
+          <t>0,42%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>2,47%</t>
+          <t>2,49%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -10391,12 +10391,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>9843</t>
+          <t>9665</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>23470</t>
+          <t>23145</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -10406,12 +10406,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>1,66%</t>
+          <t>1,63%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>3,96%</t>
+          <t>3,91%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -10426,12 +10426,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>14910</t>
+          <t>15052</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>31168</t>
+          <t>32662</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -10441,12 +10441,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>1,32%</t>
+          <t>1,33%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>2,76%</t>
+          <t>2,89%</t>
         </is>
       </c>
     </row>
@@ -10469,12 +10469,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>523104</t>
+          <t>522968</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>533955</t>
+          <t>534098</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -10484,12 +10484,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>97,53%</t>
+          <t>97,51%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>99,56%</t>
+          <t>99,58%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -10504,12 +10504,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>568532</t>
+          <t>568857</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>582159</t>
+          <t>582337</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -10519,12 +10519,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>96,04%</t>
+          <t>96,09%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>98,34%</t>
+          <t>98,37%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -10539,12 +10539,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>1097172</t>
+          <t>1095678</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>1113430</t>
+          <t>1113288</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -10554,12 +10554,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>97,24%</t>
+          <t>97,11%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>98,68%</t>
+          <t>98,67%</t>
         </is>
       </c>
     </row>
@@ -10699,12 +10699,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>7020</t>
+          <t>7787</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>35033</t>
+          <t>34571</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -10714,12 +10714,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>0,79%</t>
+          <t>0,88%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>3,95%</t>
+          <t>3,89%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -10734,12 +10734,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>14341</t>
+          <t>14706</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>29725</t>
+          <t>29008</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -10749,12 +10749,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>2,01%</t>
+          <t>2,06%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>4,17%</t>
+          <t>4,07%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -10769,12 +10769,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>23392</t>
+          <t>25690</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>55281</t>
+          <t>55916</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -10784,12 +10784,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>1,46%</t>
+          <t>1,6%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>3,45%</t>
+          <t>3,49%</t>
         </is>
       </c>
     </row>
@@ -10812,12 +10812,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>852753</t>
+          <t>853215</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>880766</t>
+          <t>879999</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -10827,12 +10827,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>96,05%</t>
+          <t>96,11%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>99,21%</t>
+          <t>99,12%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -10847,12 +10847,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>683156</t>
+          <t>683873</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>698540</t>
+          <t>698175</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -10862,12 +10862,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>95,83%</t>
+          <t>95,93%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>97,99%</t>
+          <t>97,94%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -10882,12 +10882,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>1545386</t>
+          <t>1544751</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>1577275</t>
+          <t>1574977</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -10897,12 +10897,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>96,55%</t>
+          <t>96,51%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>98,54%</t>
+          <t>98,4%</t>
         </is>
       </c>
     </row>
@@ -11042,12 +11042,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>9307</t>
+          <t>9068</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>24248</t>
+          <t>24146</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -11057,12 +11057,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>1,66%</t>
+          <t>1,62%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>4,32%</t>
+          <t>4,3%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -11077,12 +11077,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>7245</t>
+          <t>7020</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>17426</t>
+          <t>17892</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -11092,12 +11092,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>1,32%</t>
+          <t>1,28%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>3,18%</t>
+          <t>3,27%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -11112,12 +11112,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>18575</t>
+          <t>18707</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>36207</t>
+          <t>37583</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -11127,12 +11127,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>1,67%</t>
+          <t>1,69%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>3,26%</t>
+          <t>3,39%</t>
         </is>
       </c>
     </row>
@@ -11155,12 +11155,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>536986</t>
+          <t>537088</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>551927</t>
+          <t>552166</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -11170,12 +11170,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>95,68%</t>
+          <t>95,7%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>98,34%</t>
+          <t>98,38%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -11190,12 +11190,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>530479</t>
+          <t>530013</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>540660</t>
+          <t>540885</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -11205,12 +11205,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>96,82%</t>
+          <t>96,73%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>98,68%</t>
+          <t>98,72%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -11225,12 +11225,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>1072932</t>
+          <t>1071556</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>1090564</t>
+          <t>1090432</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -11240,12 +11240,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>96,74%</t>
+          <t>96,61%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>98,33%</t>
+          <t>98,31%</t>
         </is>
       </c>
     </row>
@@ -11385,12 +11385,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>5248</t>
+          <t>5558</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>15898</t>
+          <t>15889</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -11400,7 +11400,7 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>1,43%</t>
+          <t>1,51%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
@@ -11420,12 +11420,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>15568</t>
+          <t>14868</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>442748</t>
+          <t>419562</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -11435,12 +11435,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>2,56%</t>
+          <t>2,44%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>72,78%</t>
+          <t>68,97%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -11455,12 +11455,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>24431</t>
+          <t>24538</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>564763</t>
+          <t>572784</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -11470,12 +11470,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>2,5%</t>
+          <t>2,51%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>57,83%</t>
+          <t>58,65%</t>
         </is>
       </c>
     </row>
@@ -11498,12 +11498,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>352267</t>
+          <t>352276</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>362917</t>
+          <t>362607</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -11518,7 +11518,7 @@
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>98,57%</t>
+          <t>98,49%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -11533,12 +11533,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>165620</t>
+          <t>188806</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>592800</t>
+          <t>593500</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -11548,12 +11548,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>27,22%</t>
+          <t>31,03%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>97,44%</t>
+          <t>97,56%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -11568,12 +11568,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>411770</t>
+          <t>403749</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>952102</t>
+          <t>951995</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -11583,12 +11583,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>42,17%</t>
+          <t>41,35%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>97,5%</t>
+          <t>97,49%</t>
         </is>
       </c>
     </row>
@@ -11728,12 +11728,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>5194</t>
+          <t>5058</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>15065</t>
+          <t>15083</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -11743,7 +11743,7 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>1,84%</t>
+          <t>1,79%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
@@ -11763,12 +11763,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>14242</t>
+          <t>14888</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>26618</t>
+          <t>27231</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -11778,12 +11778,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>3,34%</t>
+          <t>3,5%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>6,25%</t>
+          <t>6,39%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -11798,12 +11798,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>21488</t>
+          <t>21592</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>37593</t>
+          <t>37402</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -11813,12 +11813,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>3,03%</t>
+          <t>3,05%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>5,31%</t>
+          <t>5,28%</t>
         </is>
       </c>
     </row>
@@ -11841,12 +11841,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>267694</t>
+          <t>267676</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>277565</t>
+          <t>277701</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -11861,7 +11861,7 @@
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>98,16%</t>
+          <t>98,21%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -11876,12 +11876,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>399213</t>
+          <t>398600</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>411589</t>
+          <t>410943</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -11891,12 +11891,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>93,75%</t>
+          <t>93,61%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>96,66%</t>
+          <t>96,5%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -11911,12 +11911,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>670997</t>
+          <t>671188</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>687102</t>
+          <t>686998</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -11926,12 +11926,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>94,69%</t>
+          <t>94,72%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>96,97%</t>
+          <t>96,95%</t>
         </is>
       </c>
     </row>
@@ -12071,12 +12071,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>55572</t>
+          <t>53415</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>96163</t>
+          <t>92622</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -12086,12 +12086,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>1,61%</t>
+          <t>1,54%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>2,78%</t>
+          <t>2,68%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -12106,12 +12106,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>99266</t>
+          <t>99799</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>948285</t>
+          <t>932453</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -12121,12 +12121,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>2,67%</t>
+          <t>2,69%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>25,54%</t>
+          <t>25,12%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -12141,12 +12141,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>166849</t>
+          <t>168822</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>1081122</t>
+          <t>1039504</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -12156,12 +12156,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>2,33%</t>
+          <t>2,35%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>15,07%</t>
+          <t>14,49%</t>
         </is>
       </c>
     </row>
@@ -12184,12 +12184,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>3363654</t>
+          <t>3367195</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>3404245</t>
+          <t>3406402</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -12199,12 +12199,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>97,22%</t>
+          <t>97,32%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>98,39%</t>
+          <t>98,46%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -12219,12 +12219,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>2763995</t>
+          <t>2779827</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>3613014</t>
+          <t>3612481</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -12234,12 +12234,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>74,46%</t>
+          <t>74,88%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>97,33%</t>
+          <t>97,31%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -12254,12 +12254,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>6090975</t>
+          <t>6132593</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>7005248</t>
+          <t>7003275</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -12269,12 +12269,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>84,93%</t>
+          <t>85,51%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>97,67%</t>
+          <t>97,65%</t>
         </is>
       </c>
     </row>

--- a/data/trans_orig/P2A_psíq_R-Edad-trans_orig.xlsx
+++ b/data/trans_orig/P2A_psíq_R-Edad-trans_orig.xlsx
@@ -773,7 +773,7 @@
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>4917</t>
+          <t>4910</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -808,7 +808,7 @@
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>4444</t>
+          <t>4909</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -823,7 +823,7 @@
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>0,46%</t>
+          <t>0,51%</t>
         </is>
       </c>
     </row>
@@ -881,7 +881,7 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>462572</t>
+          <t>462579</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
@@ -916,7 +916,7 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>957109</t>
+          <t>956644</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
@@ -931,7 +931,7 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>99,54%</t>
+          <t>99,49%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
@@ -1076,12 +1076,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>881</t>
+          <t>878</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>8777</t>
+          <t>8337</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -1096,7 +1096,7 @@
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>1,19%</t>
+          <t>1,13%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -1146,12 +1146,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>2073</t>
+          <t>2031</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>12268</t>
+          <t>12009</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -1166,7 +1166,7 @@
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>0,9%</t>
+          <t>0,88%</t>
         </is>
       </c>
     </row>
@@ -1189,12 +1189,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>726712</t>
+          <t>727152</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>734608</t>
+          <t>734611</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -1204,7 +1204,7 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>98,81%</t>
+          <t>98,87%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
@@ -1259,12 +1259,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>1348714</t>
+          <t>1348973</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>1358909</t>
+          <t>1358951</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -1274,7 +1274,7 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>99,1%</t>
+          <t>99,12%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
@@ -1419,12 +1419,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>1583</t>
+          <t>1585</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>13807</t>
+          <t>13173</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1439,7 +1439,7 @@
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>2,16%</t>
+          <t>2,06%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1454,12 +1454,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>3136</t>
+          <t>3044</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>14602</t>
+          <t>13769</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -1469,47 +1469,47 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
+          <t>0,44%</t>
+        </is>
+      </c>
+      <c r="P10" s="2" t="inlineStr">
+        <is>
+          <t>2,0%</t>
+        </is>
+      </c>
+      <c r="Q10" s="2" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="R10" s="2" t="inlineStr">
+        <is>
+          <t>12670</t>
+        </is>
+      </c>
+      <c r="S10" s="2" t="inlineStr">
+        <is>
+          <t>6019</t>
+        </is>
+      </c>
+      <c r="T10" s="2" t="inlineStr">
+        <is>
+          <t>22110</t>
+        </is>
+      </c>
+      <c r="U10" s="2" t="inlineStr">
+        <is>
+          <t>0,95%</t>
+        </is>
+      </c>
+      <c r="V10" s="2" t="inlineStr">
+        <is>
           <t>0,45%</t>
         </is>
       </c>
-      <c r="P10" s="2" t="inlineStr">
-        <is>
-          <t>2,12%</t>
-        </is>
-      </c>
-      <c r="Q10" s="2" t="inlineStr">
-        <is>
-          <t>11</t>
-        </is>
-      </c>
-      <c r="R10" s="2" t="inlineStr">
-        <is>
-          <t>12670</t>
-        </is>
-      </c>
-      <c r="S10" s="2" t="inlineStr">
-        <is>
-          <t>7252</t>
-        </is>
-      </c>
-      <c r="T10" s="2" t="inlineStr">
-        <is>
-          <t>22967</t>
-        </is>
-      </c>
-      <c r="U10" s="2" t="inlineStr">
-        <is>
-          <t>0,95%</t>
-        </is>
-      </c>
-      <c r="V10" s="2" t="inlineStr">
-        <is>
-          <t>0,55%</t>
-        </is>
-      </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>1,73%</t>
+          <t>1,66%</t>
         </is>
       </c>
     </row>
@@ -1532,12 +1532,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>624861</t>
+          <t>625495</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>637085</t>
+          <t>637083</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -1547,7 +1547,7 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>97,84%</t>
+          <t>97,94%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
@@ -1567,12 +1567,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>675142</t>
+          <t>675975</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>686608</t>
+          <t>686700</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -1582,47 +1582,47 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>97,88%</t>
+          <t>98,0%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
+          <t>99,56%</t>
+        </is>
+      </c>
+      <c r="Q11" s="2" t="inlineStr">
+        <is>
+          <t>1260</t>
+        </is>
+      </c>
+      <c r="R11" s="2" t="inlineStr">
+        <is>
+          <t>1315742</t>
+        </is>
+      </c>
+      <c r="S11" s="2" t="inlineStr">
+        <is>
+          <t>1306302</t>
+        </is>
+      </c>
+      <c r="T11" s="2" t="inlineStr">
+        <is>
+          <t>1322393</t>
+        </is>
+      </c>
+      <c r="U11" s="2" t="inlineStr">
+        <is>
+          <t>99,05%</t>
+        </is>
+      </c>
+      <c r="V11" s="2" t="inlineStr">
+        <is>
+          <t>98,34%</t>
+        </is>
+      </c>
+      <c r="W11" s="2" t="inlineStr">
+        <is>
           <t>99,55%</t>
-        </is>
-      </c>
-      <c r="Q11" s="2" t="inlineStr">
-        <is>
-          <t>1260</t>
-        </is>
-      </c>
-      <c r="R11" s="2" t="inlineStr">
-        <is>
-          <t>1315742</t>
-        </is>
-      </c>
-      <c r="S11" s="2" t="inlineStr">
-        <is>
-          <t>1305445</t>
-        </is>
-      </c>
-      <c r="T11" s="2" t="inlineStr">
-        <is>
-          <t>1321160</t>
-        </is>
-      </c>
-      <c r="U11" s="2" t="inlineStr">
-        <is>
-          <t>99,05%</t>
-        </is>
-      </c>
-      <c r="V11" s="2" t="inlineStr">
-        <is>
-          <t>98,27%</t>
-        </is>
-      </c>
-      <c r="W11" s="2" t="inlineStr">
-        <is>
-          <t>99,45%</t>
         </is>
       </c>
     </row>
@@ -1762,12 +1762,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>4158</t>
+          <t>4098</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>16619</t>
+          <t>17449</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -1777,12 +1777,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>0,8%</t>
+          <t>0,79%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>3,2%</t>
+          <t>3,36%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -1797,12 +1797,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>5009</t>
+          <t>4880</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>17748</t>
+          <t>17303</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -1812,12 +1812,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>0,97%</t>
+          <t>0,95%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>3,44%</t>
+          <t>3,36%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1832,12 +1832,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>10675</t>
+          <t>11720</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>28824</t>
+          <t>28692</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -1847,12 +1847,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>1,03%</t>
+          <t>1,13%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>2,79%</t>
+          <t>2,77%</t>
         </is>
       </c>
     </row>
@@ -1875,12 +1875,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>502528</t>
+          <t>501698</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>514989</t>
+          <t>515049</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1890,12 +1890,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>96,8%</t>
+          <t>96,64%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>99,2%</t>
+          <t>99,21%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -1910,12 +1910,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>497894</t>
+          <t>498339</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>510633</t>
+          <t>510762</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -1925,12 +1925,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>96,56%</t>
+          <t>96,64%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>99,03%</t>
+          <t>99,05%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1945,12 +1945,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>1005965</t>
+          <t>1006097</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>1024114</t>
+          <t>1023069</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -1960,12 +1960,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>97,21%</t>
+          <t>97,23%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>98,97%</t>
+          <t>98,87%</t>
         </is>
       </c>
     </row>
@@ -2110,7 +2110,7 @@
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>6163</t>
+          <t>6222</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -2125,42 +2125,42 @@
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
+          <t>1,61%</t>
+        </is>
+      </c>
+      <c r="J16" s="2" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="K16" s="2" t="inlineStr">
+        <is>
+          <t>6441</t>
+        </is>
+      </c>
+      <c r="L16" s="2" t="inlineStr">
+        <is>
+          <t>2454</t>
+        </is>
+      </c>
+      <c r="M16" s="2" t="inlineStr">
+        <is>
+          <t>13736</t>
+        </is>
+      </c>
+      <c r="N16" s="2" t="inlineStr">
+        <is>
           <t>1,59%</t>
         </is>
       </c>
-      <c r="J16" s="2" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
-      <c r="K16" s="2" t="inlineStr">
-        <is>
-          <t>6441</t>
-        </is>
-      </c>
-      <c r="L16" s="2" t="inlineStr">
-        <is>
-          <t>2931</t>
-        </is>
-      </c>
-      <c r="M16" s="2" t="inlineStr">
-        <is>
-          <t>14863</t>
-        </is>
-      </c>
-      <c r="N16" s="2" t="inlineStr">
-        <is>
-          <t>1,59%</t>
-        </is>
-      </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>0,73%</t>
+          <t>0,61%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>3,68%</t>
+          <t>3,4%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2175,12 +2175,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>3960</t>
+          <t>3989</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>16326</t>
+          <t>16264</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -2218,7 +2218,7 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>380547</t>
+          <t>380488</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
@@ -2233,47 +2233,47 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
+          <t>98,39%</t>
+        </is>
+      </c>
+      <c r="I17" s="2" t="inlineStr">
+        <is>
+          <t>100,0%</t>
+        </is>
+      </c>
+      <c r="J17" s="2" t="inlineStr">
+        <is>
+          <t>390</t>
+        </is>
+      </c>
+      <c r="K17" s="2" t="inlineStr">
+        <is>
+          <t>397545</t>
+        </is>
+      </c>
+      <c r="L17" s="2" t="inlineStr">
+        <is>
+          <t>390250</t>
+        </is>
+      </c>
+      <c r="M17" s="2" t="inlineStr">
+        <is>
+          <t>401532</t>
+        </is>
+      </c>
+      <c r="N17" s="2" t="inlineStr">
+        <is>
           <t>98,41%</t>
         </is>
       </c>
-      <c r="I17" s="2" t="inlineStr">
-        <is>
-          <t>100,0%</t>
-        </is>
-      </c>
-      <c r="J17" s="2" t="inlineStr">
-        <is>
-          <t>390</t>
-        </is>
-      </c>
-      <c r="K17" s="2" t="inlineStr">
-        <is>
-          <t>397545</t>
-        </is>
-      </c>
-      <c r="L17" s="2" t="inlineStr">
-        <is>
-          <t>389123</t>
-        </is>
-      </c>
-      <c r="M17" s="2" t="inlineStr">
-        <is>
-          <t>401055</t>
-        </is>
-      </c>
-      <c r="N17" s="2" t="inlineStr">
-        <is>
-          <t>98,41%</t>
-        </is>
-      </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>96,32%</t>
+          <t>96,6%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>99,27%</t>
+          <t>99,39%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2288,12 +2288,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>774370</t>
+          <t>774432</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>786736</t>
+          <t>786707</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -2448,12 +2448,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>935</t>
+          <t>944</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>9168</t>
+          <t>8382</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -2468,7 +2468,7 @@
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>3,13%</t>
+          <t>2,86%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -2483,12 +2483,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>1794</t>
+          <t>1798</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>10041</t>
+          <t>10936</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -2503,7 +2503,7 @@
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>2,93%</t>
+          <t>3,19%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -2518,12 +2518,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>4465</t>
+          <t>3747</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>15603</t>
+          <t>14571</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -2533,12 +2533,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>0,7%</t>
+          <t>0,59%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>2,46%</t>
+          <t>2,29%</t>
         </is>
       </c>
     </row>
@@ -2561,12 +2561,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>283415</t>
+          <t>284201</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>291648</t>
+          <t>291639</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -2576,7 +2576,7 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>96,87%</t>
+          <t>97,14%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
@@ -2596,12 +2596,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>332893</t>
+          <t>331998</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>341140</t>
+          <t>341136</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -2611,7 +2611,7 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>97,07%</t>
+          <t>96,81%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
@@ -2631,12 +2631,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>619914</t>
+          <t>620946</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>631052</t>
+          <t>631770</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -2646,12 +2646,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>97,54%</t>
+          <t>97,71%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>99,3%</t>
+          <t>99,41%</t>
         </is>
       </c>
     </row>
@@ -2791,12 +2791,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>2742</t>
+          <t>3338</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>14738</t>
+          <t>15331</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -2806,12 +2806,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>1,31%</t>
+          <t>1,59%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>7,02%</t>
+          <t>7,3%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -2826,12 +2826,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>3254</t>
+          <t>2737</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>15300</t>
+          <t>15501</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -2841,12 +2841,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>0,97%</t>
+          <t>0,82%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>4,58%</t>
+          <t>4,64%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -2861,12 +2861,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>8097</t>
+          <t>6911</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>24597</t>
+          <t>22740</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -2876,12 +2876,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>1,49%</t>
+          <t>1,27%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>4,52%</t>
+          <t>4,18%</t>
         </is>
       </c>
     </row>
@@ -2904,12 +2904,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>195145</t>
+          <t>194552</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>207141</t>
+          <t>206545</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -2919,12 +2919,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>92,98%</t>
+          <t>92,7%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>98,69%</t>
+          <t>98,41%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -2939,12 +2939,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>318608</t>
+          <t>318407</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>330654</t>
+          <t>331171</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -2954,12 +2954,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>95,42%</t>
+          <t>95,36%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>99,03%</t>
+          <t>99,18%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -2974,12 +2974,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>519194</t>
+          <t>521051</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>535694</t>
+          <t>536880</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -2989,12 +2989,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>95,48%</t>
+          <t>95,82%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>98,51%</t>
+          <t>98,73%</t>
         </is>
       </c>
     </row>
@@ -3134,12 +3134,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>20150</t>
+          <t>20555</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>42995</t>
+          <t>44210</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -3149,12 +3149,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>0,61%</t>
+          <t>0,63%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>1,31%</t>
+          <t>1,35%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -3169,12 +3169,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>28386</t>
+          <t>28524</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>53962</t>
+          <t>55457</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -3189,7 +3189,7 @@
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>1,6%</t>
+          <t>1,64%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -3204,12 +3204,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>54557</t>
+          <t>52846</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>87362</t>
+          <t>86909</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -3219,7 +3219,7 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>0,82%</t>
+          <t>0,79%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
@@ -3247,12 +3247,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>3233548</t>
+          <t>3232333</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>3256393</t>
+          <t>3255988</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -3262,82 +3262,82 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
+          <t>98,65%</t>
+        </is>
+      </c>
+      <c r="I26" s="2" t="inlineStr">
+        <is>
+          <t>99,37%</t>
+        </is>
+      </c>
+      <c r="J26" s="2" t="inlineStr">
+        <is>
+          <t>3258</t>
+        </is>
+      </c>
+      <c r="K26" s="2" t="inlineStr">
+        <is>
+          <t>3339721</t>
+        </is>
+      </c>
+      <c r="L26" s="2" t="inlineStr">
+        <is>
+          <t>3323740</t>
+        </is>
+      </c>
+      <c r="M26" s="2" t="inlineStr">
+        <is>
+          <t>3350673</t>
+        </is>
+      </c>
+      <c r="N26" s="2" t="inlineStr">
+        <is>
+          <t>98,83%</t>
+        </is>
+      </c>
+      <c r="O26" s="2" t="inlineStr">
+        <is>
+          <t>98,36%</t>
+        </is>
+      </c>
+      <c r="P26" s="2" t="inlineStr">
+        <is>
+          <t>99,16%</t>
+        </is>
+      </c>
+      <c r="Q26" s="2" t="inlineStr">
+        <is>
+          <t>6444</t>
+        </is>
+      </c>
+      <c r="R26" s="2" t="inlineStr">
+        <is>
+          <t>6586525</t>
+        </is>
+      </c>
+      <c r="S26" s="2" t="inlineStr">
+        <is>
+          <t>6568832</t>
+        </is>
+      </c>
+      <c r="T26" s="2" t="inlineStr">
+        <is>
+          <t>6602895</t>
+        </is>
+      </c>
+      <c r="U26" s="2" t="inlineStr">
+        <is>
+          <t>98,96%</t>
+        </is>
+      </c>
+      <c r="V26" s="2" t="inlineStr">
+        <is>
           <t>98,69%</t>
         </is>
       </c>
-      <c r="I26" s="2" t="inlineStr">
-        <is>
-          <t>99,39%</t>
-        </is>
-      </c>
-      <c r="J26" s="2" t="inlineStr">
-        <is>
-          <t>3258</t>
-        </is>
-      </c>
-      <c r="K26" s="2" t="inlineStr">
-        <is>
-          <t>3339721</t>
-        </is>
-      </c>
-      <c r="L26" s="2" t="inlineStr">
-        <is>
-          <t>3325235</t>
-        </is>
-      </c>
-      <c r="M26" s="2" t="inlineStr">
-        <is>
-          <t>3350811</t>
-        </is>
-      </c>
-      <c r="N26" s="2" t="inlineStr">
-        <is>
-          <t>98,83%</t>
-        </is>
-      </c>
-      <c r="O26" s="2" t="inlineStr">
-        <is>
-          <t>98,4%</t>
-        </is>
-      </c>
-      <c r="P26" s="2" t="inlineStr">
-        <is>
-          <t>99,16%</t>
-        </is>
-      </c>
-      <c r="Q26" s="2" t="inlineStr">
-        <is>
-          <t>6444</t>
-        </is>
-      </c>
-      <c r="R26" s="2" t="inlineStr">
-        <is>
-          <t>6586525</t>
-        </is>
-      </c>
-      <c r="S26" s="2" t="inlineStr">
-        <is>
-          <t>6568379</t>
-        </is>
-      </c>
-      <c r="T26" s="2" t="inlineStr">
-        <is>
-          <t>6601184</t>
-        </is>
-      </c>
-      <c r="U26" s="2" t="inlineStr">
-        <is>
-          <t>98,96%</t>
-        </is>
-      </c>
-      <c r="V26" s="2" t="inlineStr">
-        <is>
-          <t>98,69%</t>
-        </is>
-      </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>99,18%</t>
+          <t>99,21%</t>
         </is>
       </c>
     </row>
@@ -3712,12 +3712,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>937</t>
+          <t>939</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>7730</t>
+          <t>7457</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -3732,7 +3732,7 @@
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>1,7%</t>
+          <t>1,64%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -3747,12 +3747,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>3808</t>
+          <t>3749</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>15117</t>
+          <t>15431</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -3762,12 +3762,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>0,89%</t>
+          <t>0,87%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>3,51%</t>
+          <t>3,59%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -3782,12 +3782,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>5716</t>
+          <t>5839</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>17606</t>
+          <t>20264</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -3797,12 +3797,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>0,65%</t>
+          <t>0,66%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>1,99%</t>
+          <t>2,29%</t>
         </is>
       </c>
     </row>
@@ -3825,12 +3825,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>446416</t>
+          <t>446689</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>453209</t>
+          <t>453207</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -3840,7 +3840,7 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>98,3%</t>
+          <t>98,36%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
@@ -3860,12 +3860,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>415113</t>
+          <t>414799</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>426422</t>
+          <t>426481</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -3875,12 +3875,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>96,49%</t>
+          <t>96,41%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>99,11%</t>
+          <t>99,13%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -3895,12 +3895,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>866770</t>
+          <t>864112</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>878660</t>
+          <t>878537</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -3910,12 +3910,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>98,01%</t>
+          <t>97,71%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>99,35%</t>
+          <t>99,34%</t>
         </is>
       </c>
     </row>
@@ -4055,12 +4055,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>4703</t>
+          <t>4906</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>19566</t>
+          <t>19943</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -4070,12 +4070,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>0,68%</t>
+          <t>0,71%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>2,85%</t>
+          <t>2,9%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -4090,12 +4090,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>1912</t>
+          <t>1889</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>13173</t>
+          <t>14232</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -4110,7 +4110,7 @@
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>2,16%</t>
+          <t>2,33%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -4125,12 +4125,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>8913</t>
+          <t>8535</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>25886</t>
+          <t>26663</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -4140,12 +4140,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>0,69%</t>
+          <t>0,66%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>2,0%</t>
+          <t>2,06%</t>
         </is>
       </c>
     </row>
@@ -4168,12 +4168,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>667521</t>
+          <t>667144</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>682384</t>
+          <t>682181</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -4183,12 +4183,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>97,15%</t>
+          <t>97,1%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>99,32%</t>
+          <t>99,29%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -4203,12 +4203,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>597082</t>
+          <t>596023</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>608343</t>
+          <t>608366</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -4218,7 +4218,7 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>97,84%</t>
+          <t>97,67%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
@@ -4238,12 +4238,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>1271456</t>
+          <t>1270679</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>1288429</t>
+          <t>1288807</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -4253,12 +4253,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>98,0%</t>
+          <t>97,94%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>99,31%</t>
+          <t>99,34%</t>
         </is>
       </c>
     </row>
@@ -4398,12 +4398,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>3787</t>
+          <t>3756</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>17547</t>
+          <t>19119</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -4413,12 +4413,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>0,56%</t>
+          <t>0,55%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>2,57%</t>
+          <t>2,8%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -4433,12 +4433,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>14072</t>
+          <t>12835</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>34198</t>
+          <t>32502</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -4448,12 +4448,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>1,98%</t>
+          <t>1,81%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>4,81%</t>
+          <t>4,57%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -4468,12 +4468,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>19826</t>
+          <t>20470</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>43789</t>
+          <t>43881</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -4483,12 +4483,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>1,42%</t>
+          <t>1,47%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>3,14%</t>
+          <t>3,15%</t>
         </is>
       </c>
     </row>
@@ -4511,12 +4511,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>664316</t>
+          <t>662744</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>678076</t>
+          <t>678107</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -4526,12 +4526,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>97,43%</t>
+          <t>97,2%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>99,44%</t>
+          <t>99,45%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -4546,12 +4546,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>676652</t>
+          <t>678348</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>696778</t>
+          <t>698015</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -4561,12 +4561,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>95,19%</t>
+          <t>95,43%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>98,02%</t>
+          <t>98,19%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -4581,12 +4581,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>1348923</t>
+          <t>1348831</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>1372886</t>
+          <t>1372242</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -4596,12 +4596,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>96,86%</t>
+          <t>96,85%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>98,58%</t>
+          <t>98,53%</t>
         </is>
       </c>
     </row>
@@ -4741,12 +4741,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>6377</t>
+          <t>6212</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>23502</t>
+          <t>25022</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -4756,12 +4756,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>1,04%</t>
+          <t>1,01%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>3,82%</t>
+          <t>4,07%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -4776,12 +4776,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>8436</t>
+          <t>9498</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>24584</t>
+          <t>25963</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -4791,12 +4791,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>1,37%</t>
+          <t>1,54%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>3,99%</t>
+          <t>4,21%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -4811,12 +4811,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>19680</t>
+          <t>18811</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>40472</t>
+          <t>41605</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -4826,12 +4826,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>1,6%</t>
+          <t>1,53%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>3,29%</t>
+          <t>3,38%</t>
         </is>
       </c>
     </row>
@@ -4854,12 +4854,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>591115</t>
+          <t>589595</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>608240</t>
+          <t>608405</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -4869,12 +4869,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>96,18%</t>
+          <t>95,93%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>98,96%</t>
+          <t>98,99%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -4889,12 +4889,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>591615</t>
+          <t>590236</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>607763</t>
+          <t>606701</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -4904,12 +4904,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>96,01%</t>
+          <t>95,79%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>98,63%</t>
+          <t>98,46%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -4924,12 +4924,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>1190344</t>
+          <t>1189211</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>1211136</t>
+          <t>1212005</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -4939,12 +4939,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>96,71%</t>
+          <t>96,62%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>98,4%</t>
+          <t>98,47%</t>
         </is>
       </c>
     </row>
@@ -5084,12 +5084,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>5784</t>
+          <t>5311</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>20982</t>
+          <t>19263</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -5099,12 +5099,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>1,35%</t>
+          <t>1,24%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>4,89%</t>
+          <t>4,49%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -5119,12 +5119,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>4983</t>
+          <t>4518</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>18411</t>
+          <t>19236</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -5134,12 +5134,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>1,11%</t>
+          <t>1,01%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>4,11%</t>
+          <t>4,3%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -5154,12 +5154,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>12105</t>
+          <t>12447</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>31361</t>
+          <t>30796</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -5169,12 +5169,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>1,38%</t>
+          <t>1,42%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>3,58%</t>
+          <t>3,51%</t>
         </is>
       </c>
     </row>
@@ -5197,12 +5197,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>408447</t>
+          <t>410166</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>423645</t>
+          <t>424118</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -5212,12 +5212,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>95,11%</t>
+          <t>95,51%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>98,65%</t>
+          <t>98,76%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -5232,12 +5232,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>429389</t>
+          <t>428564</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>442817</t>
+          <t>443282</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -5247,12 +5247,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>95,89%</t>
+          <t>95,7%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>98,89%</t>
+          <t>98,99%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -5267,12 +5267,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>845868</t>
+          <t>846433</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>865124</t>
+          <t>864782</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -5282,12 +5282,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>96,42%</t>
+          <t>96,49%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>98,62%</t>
+          <t>98,58%</t>
         </is>
       </c>
     </row>
@@ -5427,12 +5427,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>4849</t>
+          <t>4090</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>18766</t>
+          <t>17890</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -5442,12 +5442,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>1,57%</t>
+          <t>1,32%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>6,06%</t>
+          <t>5,77%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -5462,12 +5462,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>970</t>
+          <t>965</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>11659</t>
+          <t>10918</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -5482,7 +5482,7 @@
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>3,29%</t>
+          <t>3,08%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -5497,12 +5497,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>6843</t>
+          <t>7422</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>23016</t>
+          <t>23496</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -5512,12 +5512,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>1,03%</t>
+          <t>1,12%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>3,47%</t>
+          <t>3,54%</t>
         </is>
       </c>
     </row>
@@ -5540,12 +5540,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>291020</t>
+          <t>291896</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>304937</t>
+          <t>305696</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -5555,12 +5555,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>93,94%</t>
+          <t>94,23%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>98,43%</t>
+          <t>98,68%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -5575,12 +5575,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>342337</t>
+          <t>343078</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>353026</t>
+          <t>353031</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -5590,7 +5590,7 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>96,71%</t>
+          <t>96,92%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
@@ -5610,12 +5610,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>640766</t>
+          <t>640286</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>656939</t>
+          <t>656360</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -5625,12 +5625,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>96,53%</t>
+          <t>96,46%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>98,97%</t>
+          <t>98,88%</t>
         </is>
       </c>
     </row>
@@ -5770,12 +5770,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>3246</t>
+          <t>3297</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>17627</t>
+          <t>17440</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -5785,12 +5785,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>1,3%</t>
+          <t>1,32%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>7,05%</t>
+          <t>6,98%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -5805,12 +5805,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>4363</t>
+          <t>5354</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>17464</t>
+          <t>18411</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -5820,12 +5820,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>1,12%</t>
+          <t>1,38%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>4,49%</t>
+          <t>4,73%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -5840,12 +5840,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>10614</t>
+          <t>10741</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>28962</t>
+          <t>29472</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -5855,12 +5855,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>1,66%</t>
+          <t>1,68%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>4,53%</t>
+          <t>4,61%</t>
         </is>
       </c>
     </row>
@@ -5883,12 +5883,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>232224</t>
+          <t>232411</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>246605</t>
+          <t>246554</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -5898,12 +5898,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>92,95%</t>
+          <t>93,02%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>98,7%</t>
+          <t>98,68%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -5918,12 +5918,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>371515</t>
+          <t>370568</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>384616</t>
+          <t>383625</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -5933,12 +5933,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>95,51%</t>
+          <t>95,27%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>98,88%</t>
+          <t>98,62%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -5953,12 +5953,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>609868</t>
+          <t>609358</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>628216</t>
+          <t>628089</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -5968,12 +5968,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>95,47%</t>
+          <t>95,39%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>98,34%</t>
+          <t>98,32%</t>
         </is>
       </c>
     </row>
@@ -6113,12 +6113,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>48781</t>
+          <t>48481</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>85110</t>
+          <t>83120</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -6128,12 +6128,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>1,42%</t>
+          <t>1,41%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>2,48%</t>
+          <t>2,43%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -6148,12 +6148,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>59306</t>
+          <t>58689</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>92986</t>
+          <t>93319</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -6163,12 +6163,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>1,67%</t>
+          <t>1,65%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>2,61%</t>
+          <t>2,62%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -6183,12 +6183,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>114140</t>
+          <t>114989</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>162553</t>
+          <t>163756</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -6198,12 +6198,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>1,63%</t>
+          <t>1,65%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>2,33%</t>
+          <t>2,34%</t>
         </is>
       </c>
     </row>
@@ -6226,12 +6226,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>3341669</t>
+          <t>3343659</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>3377998</t>
+          <t>3378298</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -6241,12 +6241,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>97,52%</t>
+          <t>97,57%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>98,58%</t>
+          <t>98,59%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -6261,12 +6261,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>3465323</t>
+          <t>3464990</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>3499003</t>
+          <t>3499620</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -6276,12 +6276,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>97,39%</t>
+          <t>97,38%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>98,33%</t>
+          <t>98,35%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -6296,12 +6296,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>6822535</t>
+          <t>6821332</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>6870948</t>
+          <t>6870099</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -6311,12 +6311,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>97,67%</t>
+          <t>97,66%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>98,37%</t>
+          <t>98,35%</t>
         </is>
       </c>
     </row>
@@ -6696,7 +6696,7 @@
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>9446</t>
+          <t>8421</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -6711,7 +6711,7 @@
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>2,25%</t>
+          <t>2,01%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -6731,7 +6731,7 @@
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>6364</t>
+          <t>6731</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -6746,7 +6746,7 @@
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>1,61%</t>
+          <t>1,7%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -6761,12 +6761,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>1396</t>
+          <t>1079</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>11689</t>
+          <t>10983</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -6776,12 +6776,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>0,17%</t>
+          <t>0,13%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>1,43%</t>
+          <t>1,35%</t>
         </is>
       </c>
     </row>
@@ -6804,7 +6804,7 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>410017</t>
+          <t>411042</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
@@ -6819,7 +6819,7 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>97,75%</t>
+          <t>97,99%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
@@ -6839,7 +6839,7 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>389391</t>
+          <t>389024</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
@@ -6854,7 +6854,7 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>98,39%</t>
+          <t>98,3%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
@@ -6874,12 +6874,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>803529</t>
+          <t>804235</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>813822</t>
+          <t>814139</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -6889,12 +6889,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>98,57%</t>
+          <t>98,65%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>99,83%</t>
+          <t>99,87%</t>
         </is>
       </c>
     </row>
@@ -7034,12 +7034,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>1875</t>
+          <t>1866</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>12079</t>
+          <t>10560</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -7054,44 +7054,44 @@
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
+          <t>1,79%</t>
+        </is>
+      </c>
+      <c r="J7" s="2" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="K7" s="2" t="inlineStr">
+        <is>
+          <t>5706</t>
+        </is>
+      </c>
+      <c r="L7" s="2" t="inlineStr">
+        <is>
+          <t>1949</t>
+        </is>
+      </c>
+      <c r="M7" s="2" t="inlineStr">
+        <is>
+          <t>11529</t>
+        </is>
+      </c>
+      <c r="N7" s="2" t="inlineStr">
+        <is>
+          <t>1,01%</t>
+        </is>
+      </c>
+      <c r="O7" s="2" t="inlineStr">
+        <is>
+          <t>0,35%</t>
+        </is>
+      </c>
+      <c r="P7" s="2" t="inlineStr">
+        <is>
           <t>2,05%</t>
         </is>
       </c>
-      <c r="J7" s="2" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
-      <c r="K7" s="2" t="inlineStr">
-        <is>
-          <t>5706</t>
-        </is>
-      </c>
-      <c r="L7" s="2" t="inlineStr">
-        <is>
-          <t>2005</t>
-        </is>
-      </c>
-      <c r="M7" s="2" t="inlineStr">
-        <is>
-          <t>11630</t>
-        </is>
-      </c>
-      <c r="N7" s="2" t="inlineStr">
-        <is>
-          <t>1,01%</t>
-        </is>
-      </c>
-      <c r="O7" s="2" t="inlineStr">
-        <is>
-          <t>0,36%</t>
-        </is>
-      </c>
-      <c r="P7" s="2" t="inlineStr">
-        <is>
-          <t>2,06%</t>
-        </is>
-      </c>
       <c r="Q7" s="2" t="inlineStr">
         <is>
           <t>11</t>
@@ -7104,12 +7104,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>5581</t>
+          <t>5343</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>17165</t>
+          <t>18084</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -7119,12 +7119,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>0,48%</t>
+          <t>0,46%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>1,49%</t>
+          <t>1,57%</t>
         </is>
       </c>
     </row>
@@ -7147,12 +7147,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>578417</t>
+          <t>579936</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>588621</t>
+          <t>588630</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -7162,47 +7162,47 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
+          <t>98,21%</t>
+        </is>
+      </c>
+      <c r="I8" s="2" t="inlineStr">
+        <is>
+          <t>99,68%</t>
+        </is>
+      </c>
+      <c r="J8" s="2" t="inlineStr">
+        <is>
+          <t>573</t>
+        </is>
+      </c>
+      <c r="K8" s="2" t="inlineStr">
+        <is>
+          <t>557838</t>
+        </is>
+      </c>
+      <c r="L8" s="2" t="inlineStr">
+        <is>
+          <t>552015</t>
+        </is>
+      </c>
+      <c r="M8" s="2" t="inlineStr">
+        <is>
+          <t>561595</t>
+        </is>
+      </c>
+      <c r="N8" s="2" t="inlineStr">
+        <is>
+          <t>98,99%</t>
+        </is>
+      </c>
+      <c r="O8" s="2" t="inlineStr">
+        <is>
           <t>97,95%</t>
         </is>
       </c>
-      <c r="I8" s="2" t="inlineStr">
-        <is>
-          <t>99,68%</t>
-        </is>
-      </c>
-      <c r="J8" s="2" t="inlineStr">
-        <is>
-          <t>573</t>
-        </is>
-      </c>
-      <c r="K8" s="2" t="inlineStr">
-        <is>
-          <t>557838</t>
-        </is>
-      </c>
-      <c r="L8" s="2" t="inlineStr">
-        <is>
-          <t>551914</t>
-        </is>
-      </c>
-      <c r="M8" s="2" t="inlineStr">
-        <is>
-          <t>561539</t>
-        </is>
-      </c>
-      <c r="N8" s="2" t="inlineStr">
-        <is>
-          <t>98,99%</t>
-        </is>
-      </c>
-      <c r="O8" s="2" t="inlineStr">
-        <is>
-          <t>97,94%</t>
-        </is>
-      </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>99,64%</t>
+          <t>99,65%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -7217,12 +7217,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>1136875</t>
+          <t>1135956</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>1148459</t>
+          <t>1148697</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -7232,12 +7232,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>98,51%</t>
+          <t>98,43%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>99,52%</t>
+          <t>99,54%</t>
         </is>
       </c>
     </row>
@@ -7377,12 +7377,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>898</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>7576</t>
+          <t>8296</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -7392,12 +7392,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>0,13%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>1,13%</t>
+          <t>1,24%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -7412,12 +7412,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>4652</t>
+          <t>3814</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>16074</t>
+          <t>15431</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -7427,12 +7427,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>0,7%</t>
+          <t>0,58%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>2,43%</t>
+          <t>2,33%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -7447,12 +7447,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>6280</t>
+          <t>5688</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>19240</t>
+          <t>18963</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -7462,12 +7462,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>0,47%</t>
+          <t>0,43%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>1,45%</t>
+          <t>1,43%</t>
         </is>
       </c>
     </row>
@@ -7490,12 +7490,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>661521</t>
+          <t>660801</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>669097</t>
+          <t>668199</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -7505,12 +7505,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>98,87%</t>
+          <t>98,76%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>100,0%</t>
+          <t>99,87%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -7525,12 +7525,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>645312</t>
+          <t>645955</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>656734</t>
+          <t>657572</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -7540,12 +7540,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>97,57%</t>
+          <t>97,67%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>99,3%</t>
+          <t>99,42%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -7560,12 +7560,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>1311243</t>
+          <t>1311520</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>1324203</t>
+          <t>1324795</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -7575,12 +7575,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>98,55%</t>
+          <t>98,57%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>99,53%</t>
+          <t>99,57%</t>
         </is>
       </c>
     </row>
@@ -7720,12 +7720,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>2201</t>
+          <t>2855</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>14524</t>
+          <t>14794</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -7735,12 +7735,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>0,34%</t>
+          <t>0,44%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>2,25%</t>
+          <t>2,29%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -7755,12 +7755,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>4063</t>
+          <t>4185</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>16257</t>
+          <t>16472</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -7770,12 +7770,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>0,63%</t>
+          <t>0,64%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>2,5%</t>
+          <t>2,54%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -7790,12 +7790,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>9034</t>
+          <t>8714</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>25824</t>
+          <t>25992</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -7805,12 +7805,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>0,7%</t>
+          <t>0,67%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>1,99%</t>
+          <t>2,01%</t>
         </is>
       </c>
     </row>
@@ -7833,12 +7833,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>631524</t>
+          <t>631254</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>643847</t>
+          <t>643193</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -7848,12 +7848,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>97,75%</t>
+          <t>97,71%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>99,66%</t>
+          <t>99,56%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -7868,12 +7868,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>632820</t>
+          <t>632605</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>645014</t>
+          <t>644892</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -7883,12 +7883,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>97,5%</t>
+          <t>97,46%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>99,37%</t>
+          <t>99,36%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -7903,12 +7903,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>1269301</t>
+          <t>1269133</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>1286091</t>
+          <t>1286411</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -7918,12 +7918,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>98,01%</t>
+          <t>97,99%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>99,3%</t>
+          <t>99,33%</t>
         </is>
       </c>
     </row>
@@ -8063,12 +8063,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>3029</t>
+          <t>2947</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>15662</t>
+          <t>14945</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -8078,12 +8078,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>0,63%</t>
+          <t>0,62%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>3,28%</t>
+          <t>3,13%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -8098,12 +8098,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>5163</t>
+          <t>6271</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>22132</t>
+          <t>22517</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -8113,12 +8113,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>1,04%</t>
+          <t>1,26%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>4,45%</t>
+          <t>4,53%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -8133,12 +8133,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>11495</t>
+          <t>10568</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>32722</t>
+          <t>30514</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -8148,12 +8148,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>1,18%</t>
+          <t>1,08%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>3,36%</t>
+          <t>3,13%</t>
         </is>
       </c>
     </row>
@@ -8176,12 +8176,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>462256</t>
+          <t>462973</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>474889</t>
+          <t>474971</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -8191,12 +8191,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>96,72%</t>
+          <t>96,87%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>99,37%</t>
+          <t>99,38%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -8211,12 +8211,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>474717</t>
+          <t>474332</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>491686</t>
+          <t>490578</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -8226,12 +8226,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>95,55%</t>
+          <t>95,47%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>98,96%</t>
+          <t>98,74%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -8246,12 +8246,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>942045</t>
+          <t>944253</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>963272</t>
+          <t>964199</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -8261,12 +8261,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>96,64%</t>
+          <t>96,87%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>98,82%</t>
+          <t>98,92%</t>
         </is>
       </c>
     </row>
@@ -8406,12 +8406,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>1928</t>
+          <t>2817</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>11754</t>
+          <t>11640</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -8421,12 +8421,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>0,58%</t>
+          <t>0,84%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>3,52%</t>
+          <t>3,48%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -8441,12 +8441,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>4696</t>
+          <t>4831</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>17729</t>
+          <t>17997</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -8456,12 +8456,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>1,24%</t>
+          <t>1,28%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>4,69%</t>
+          <t>4,76%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -8476,12 +8476,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>8825</t>
+          <t>9059</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>24857</t>
+          <t>26143</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -8491,12 +8491,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>1,24%</t>
+          <t>1,27%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>3,49%</t>
+          <t>3,67%</t>
         </is>
       </c>
     </row>
@@ -8519,12 +8519,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>322576</t>
+          <t>322690</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>332402</t>
+          <t>331513</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -8534,12 +8534,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>96,48%</t>
+          <t>96,52%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>99,42%</t>
+          <t>99,16%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -8554,12 +8554,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>360033</t>
+          <t>359765</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>373066</t>
+          <t>372931</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -8569,12 +8569,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>95,31%</t>
+          <t>95,24%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>98,76%</t>
+          <t>98,72%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -8589,12 +8589,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>687235</t>
+          <t>685949</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>703267</t>
+          <t>703033</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -8604,12 +8604,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>96,51%</t>
+          <t>96,33%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>98,76%</t>
+          <t>98,73%</t>
         </is>
       </c>
     </row>
@@ -8754,7 +8754,7 @@
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>5006</t>
+          <t>5702</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -8769,7 +8769,7 @@
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>1,95%</t>
+          <t>2,22%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -8784,12 +8784,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>4819</t>
+          <t>4961</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>19539</t>
+          <t>19088</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -8799,12 +8799,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>1,2%</t>
+          <t>1,24%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>4,88%</t>
+          <t>4,77%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -8819,12 +8819,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>6184</t>
+          <t>5830</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>21556</t>
+          <t>20837</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -8834,12 +8834,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>0,94%</t>
+          <t>0,89%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>3,28%</t>
+          <t>3,17%</t>
         </is>
       </c>
     </row>
@@ -8862,7 +8862,7 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>251992</t>
+          <t>251296</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
@@ -8877,7 +8877,7 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>98,05%</t>
+          <t>97,78%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
@@ -8897,12 +8897,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>380630</t>
+          <t>381081</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>395350</t>
+          <t>395208</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -8912,12 +8912,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>95,12%</t>
+          <t>95,23%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>98,8%</t>
+          <t>98,76%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -8932,12 +8932,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>635611</t>
+          <t>636330</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>650983</t>
+          <t>651337</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -8947,12 +8947,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>96,72%</t>
+          <t>96,83%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>99,06%</t>
+          <t>99,11%</t>
         </is>
       </c>
     </row>
@@ -9092,12 +9092,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>21114</t>
+          <t>21819</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>46130</t>
+          <t>44714</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -9107,12 +9107,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>0,62%</t>
+          <t>0,64%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>1,36%</t>
+          <t>1,32%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -9127,12 +9127,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>42883</t>
+          <t>42859</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>74139</t>
+          <t>73940</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -9162,12 +9162,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>71741</t>
+          <t>71447</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>113052</t>
+          <t>109788</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -9182,7 +9182,7 @@
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>1,63%</t>
+          <t>1,58%</t>
         </is>
       </c>
     </row>
@@ -9205,12 +9205,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>3348220</t>
+          <t>3349636</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>3373236</t>
+          <t>3372531</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -9220,12 +9220,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>98,64%</t>
+          <t>98,68%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>99,38%</t>
+          <t>99,36%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -9240,12 +9240,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>3470403</t>
+          <t>3470602</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>3501659</t>
+          <t>3501683</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -9275,12 +9275,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>6825840</t>
+          <t>6829104</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>6867151</t>
+          <t>6867445</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -9290,7 +9290,7 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>98,37%</t>
+          <t>98,42%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
@@ -9665,32 +9665,32 @@
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>8349</t>
+          <t>11053</t>
         </is>
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>1921</t>
+          <t>3637</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>27667</t>
+          <t>24516</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
         <is>
-          <t>2,09%</t>
+          <t>2,71%</t>
         </is>
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>0,48%</t>
+          <t>0,89%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>6,92%</t>
+          <t>6,01%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -9700,32 +9700,32 @@
       </c>
       <c r="K4" s="2" t="inlineStr">
         <is>
-          <t>6092</t>
+          <t>8510</t>
         </is>
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>1349</t>
+          <t>2293</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>18901</t>
+          <t>21502</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
         <is>
-          <t>1,95%</t>
+          <t>2,35%</t>
         </is>
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>0,43%</t>
+          <t>0,63%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>6,03%</t>
+          <t>5,93%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -9735,32 +9735,32 @@
       </c>
       <c r="R4" s="2" t="inlineStr">
         <is>
-          <t>14440</t>
+          <t>19564</t>
         </is>
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>5482</t>
+          <t>9559</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>31147</t>
+          <t>37353</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
         <is>
-          <t>2,02%</t>
+          <t>2,54%</t>
         </is>
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>0,77%</t>
+          <t>1,24%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>4,37%</t>
+          <t>4,85%</t>
         </is>
       </c>
     </row>
@@ -9778,32 +9778,32 @@
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>391638</t>
+          <t>396740</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>372320</t>
+          <t>383277</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>398066</t>
+          <t>404156</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>97,91%</t>
+          <t>97,29%</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>93,08%</t>
+          <t>93,99%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>99,52%</t>
+          <t>99,11%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -9813,32 +9813,32 @@
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>307108</t>
+          <t>354002</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>294299</t>
+          <t>341010</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>311851</t>
+          <t>360219</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>98,05%</t>
+          <t>97,65%</t>
         </is>
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>93,97%</t>
+          <t>94,07%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>99,57%</t>
+          <t>99,37%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -9848,32 +9848,32 @@
       </c>
       <c r="R5" s="2" t="inlineStr">
         <is>
-          <t>698747</t>
+          <t>750741</t>
         </is>
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>682040</t>
+          <t>732952</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>707705</t>
+          <t>760746</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
         <is>
-          <t>97,98%</t>
+          <t>97,46%</t>
         </is>
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>95,63%</t>
+          <t>95,15%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>99,23%</t>
+          <t>98,76%</t>
         </is>
       </c>
     </row>
@@ -9891,17 +9891,17 @@
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>399987</t>
+          <t>407793</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>399987</t>
+          <t>407793</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>399987</t>
+          <t>407793</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -9926,17 +9926,17 @@
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>313200</t>
+          <t>362512</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>313200</t>
+          <t>362512</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>313200</t>
+          <t>362512</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -9961,17 +9961,17 @@
       </c>
       <c r="R6" s="2" t="inlineStr">
         <is>
-          <t>713187</t>
+          <t>770305</t>
         </is>
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>713187</t>
+          <t>770305</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>713187</t>
+          <t>770305</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -10008,22 +10008,22 @@
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>4148</t>
+          <t>4363</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>1078</t>
+          <t>1190</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>11386</t>
+          <t>11937</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>0,98%</t>
+          <t>0,91%</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
@@ -10033,7 +10033,7 @@
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>2,69%</t>
+          <t>2,5%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -10043,32 +10043,32 @@
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>13657</t>
+          <t>14163</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>6395</t>
+          <t>6985</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>25982</t>
+          <t>25046</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>2,67%</t>
+          <t>2,82%</t>
         </is>
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>1,25%</t>
+          <t>1,39%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>5,07%</t>
+          <t>4,99%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -10078,32 +10078,32 @@
       </c>
       <c r="R7" s="2" t="inlineStr">
         <is>
-          <t>17805</t>
+          <t>18525</t>
         </is>
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>9443</t>
+          <t>11118</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>31170</t>
+          <t>30416</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
         <is>
-          <t>1,9%</t>
+          <t>1,89%</t>
         </is>
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>1,01%</t>
+          <t>1,14%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>3,33%</t>
+          <t>3,11%</t>
         </is>
       </c>
     </row>
@@ -10121,27 +10121,27 @@
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>419399</t>
+          <t>472527</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>412161</t>
+          <t>464953</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>422469</t>
+          <t>475700</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
         <is>
-          <t>99,02%</t>
+          <t>99,09%</t>
         </is>
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>97,31%</t>
+          <t>97,5%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
@@ -10156,32 +10156,32 @@
       </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
-          <t>498436</t>
+          <t>487570</t>
         </is>
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>486111</t>
+          <t>476687</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>505698</t>
+          <t>494748</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>97,33%</t>
+          <t>97,18%</t>
         </is>
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>94,93%</t>
+          <t>95,01%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>98,75%</t>
+          <t>98,61%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -10191,32 +10191,32 @@
       </c>
       <c r="R8" s="2" t="inlineStr">
         <is>
-          <t>917835</t>
+          <t>960098</t>
         </is>
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>904470</t>
+          <t>948207</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>926197</t>
+          <t>967505</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
         <is>
-          <t>98,1%</t>
+          <t>98,11%</t>
         </is>
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>96,67%</t>
+          <t>96,89%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>98,99%</t>
+          <t>98,86%</t>
         </is>
       </c>
     </row>
@@ -10234,17 +10234,17 @@
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>423547</t>
+          <t>476890</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>423547</t>
+          <t>476890</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>423547</t>
+          <t>476890</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -10269,17 +10269,17 @@
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>512093</t>
+          <t>501733</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>512093</t>
+          <t>501733</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>512093</t>
+          <t>501733</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -10304,17 +10304,17 @@
       </c>
       <c r="R9" s="2" t="inlineStr">
         <is>
-          <t>935640</t>
+          <t>978623</t>
         </is>
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>935640</t>
+          <t>978623</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>935640</t>
+          <t>978623</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -10351,32 +10351,32 @@
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>6344</t>
+          <t>8356</t>
         </is>
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>2240</t>
+          <t>3422</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>13370</t>
+          <t>15626</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
         <is>
-          <t>1,18%</t>
+          <t>1,35%</t>
         </is>
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>0,42%</t>
+          <t>0,55%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>2,49%</t>
+          <t>2,52%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -10386,32 +10386,32 @@
       </c>
       <c r="K10" s="2" t="inlineStr">
         <is>
-          <t>15399</t>
+          <t>19639</t>
         </is>
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>9665</t>
+          <t>12508</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>23145</t>
+          <t>28041</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
         <is>
-          <t>2,6%</t>
+          <t>3,15%</t>
         </is>
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>1,63%</t>
+          <t>2,01%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>3,91%</t>
+          <t>4,5%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -10421,32 +10421,32 @@
       </c>
       <c r="R10" s="2" t="inlineStr">
         <is>
-          <t>21744</t>
+          <t>27995</t>
         </is>
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>15052</t>
+          <t>20549</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>32662</t>
+          <t>39754</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
         <is>
-          <t>1,93%</t>
+          <t>2,25%</t>
         </is>
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>1,33%</t>
+          <t>1,65%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>2,89%</t>
+          <t>3,2%</t>
         </is>
       </c>
     </row>
@@ -10464,32 +10464,32 @@
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>529994</t>
+          <t>612481</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>522968</t>
+          <t>605211</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>534098</t>
+          <t>617415</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>98,82%</t>
+          <t>98,65%</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>97,51%</t>
+          <t>97,48%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>99,58%</t>
+          <t>99,45%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -10499,32 +10499,32 @@
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>576603</t>
+          <t>603554</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>568857</t>
+          <t>595152</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>582337</t>
+          <t>610685</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>97,4%</t>
+          <t>96,85%</t>
         </is>
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>96,09%</t>
+          <t>95,5%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>98,37%</t>
+          <t>97,99%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -10534,32 +10534,32 @@
       </c>
       <c r="R11" s="2" t="inlineStr">
         <is>
-          <t>1106596</t>
+          <t>1216034</t>
         </is>
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>1095678</t>
+          <t>1204275</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>1113288</t>
+          <t>1223480</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
         <is>
-          <t>98,07%</t>
+          <t>97,75%</t>
         </is>
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>97,11%</t>
+          <t>96,8%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>98,67%</t>
+          <t>98,35%</t>
         </is>
       </c>
     </row>
@@ -10577,17 +10577,17 @@
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>536338</t>
+          <t>620837</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>536338</t>
+          <t>620837</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>536338</t>
+          <t>620837</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -10612,17 +10612,17 @@
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>592002</t>
+          <t>623193</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>592002</t>
+          <t>623193</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>592002</t>
+          <t>623193</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -10647,17 +10647,17 @@
       </c>
       <c r="R12" s="2" t="inlineStr">
         <is>
-          <t>1128340</t>
+          <t>1244029</t>
         </is>
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>1128340</t>
+          <t>1244029</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>1128340</t>
+          <t>1244029</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -10694,102 +10694,102 @@
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>20353</t>
+          <t>20639</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>7787</t>
+          <t>13279</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>34571</t>
+          <t>32383</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
+          <t>2,95%</t>
+        </is>
+      </c>
+      <c r="H13" s="2" t="inlineStr">
+        <is>
+          <t>1,9%</t>
+        </is>
+      </c>
+      <c r="I13" s="2" t="inlineStr">
+        <is>
+          <t>4,62%</t>
+        </is>
+      </c>
+      <c r="J13" s="2" t="inlineStr">
+        <is>
+          <t>33</t>
+        </is>
+      </c>
+      <c r="K13" s="2" t="inlineStr">
+        <is>
+          <t>22139</t>
+        </is>
+      </c>
+      <c r="L13" s="2" t="inlineStr">
+        <is>
+          <t>15709</t>
+        </is>
+      </c>
+      <c r="M13" s="2" t="inlineStr">
+        <is>
+          <t>31087</t>
+        </is>
+      </c>
+      <c r="N13" s="2" t="inlineStr">
+        <is>
+          <t>3,0%</t>
+        </is>
+      </c>
+      <c r="O13" s="2" t="inlineStr">
+        <is>
+          <t>2,13%</t>
+        </is>
+      </c>
+      <c r="P13" s="2" t="inlineStr">
+        <is>
+          <t>4,22%</t>
+        </is>
+      </c>
+      <c r="Q13" s="2" t="inlineStr">
+        <is>
+          <t>53</t>
+        </is>
+      </c>
+      <c r="R13" s="2" t="inlineStr">
+        <is>
+          <t>42778</t>
+        </is>
+      </c>
+      <c r="S13" s="2" t="inlineStr">
+        <is>
+          <t>32851</t>
+        </is>
+      </c>
+      <c r="T13" s="2" t="inlineStr">
+        <is>
+          <t>55914</t>
+        </is>
+      </c>
+      <c r="U13" s="2" t="inlineStr">
+        <is>
+          <t>2,98%</t>
+        </is>
+      </c>
+      <c r="V13" s="2" t="inlineStr">
+        <is>
           <t>2,29%</t>
         </is>
       </c>
-      <c r="H13" s="2" t="inlineStr">
-        <is>
-          <t>0,88%</t>
-        </is>
-      </c>
-      <c r="I13" s="2" t="inlineStr">
+      <c r="W13" s="2" t="inlineStr">
         <is>
           <t>3,89%</t>
-        </is>
-      </c>
-      <c r="J13" s="2" t="inlineStr">
-        <is>
-          <t>33</t>
-        </is>
-      </c>
-      <c r="K13" s="2" t="inlineStr">
-        <is>
-          <t>20744</t>
-        </is>
-      </c>
-      <c r="L13" s="2" t="inlineStr">
-        <is>
-          <t>14706</t>
-        </is>
-      </c>
-      <c r="M13" s="2" t="inlineStr">
-        <is>
-          <t>29008</t>
-        </is>
-      </c>
-      <c r="N13" s="2" t="inlineStr">
-        <is>
-          <t>2,91%</t>
-        </is>
-      </c>
-      <c r="O13" s="2" t="inlineStr">
-        <is>
-          <t>2,06%</t>
-        </is>
-      </c>
-      <c r="P13" s="2" t="inlineStr">
-        <is>
-          <t>4,07%</t>
-        </is>
-      </c>
-      <c r="Q13" s="2" t="inlineStr">
-        <is>
-          <t>53</t>
-        </is>
-      </c>
-      <c r="R13" s="2" t="inlineStr">
-        <is>
-          <t>41097</t>
-        </is>
-      </c>
-      <c r="S13" s="2" t="inlineStr">
-        <is>
-          <t>25690</t>
-        </is>
-      </c>
-      <c r="T13" s="2" t="inlineStr">
-        <is>
-          <t>55916</t>
-        </is>
-      </c>
-      <c r="U13" s="2" t="inlineStr">
-        <is>
-          <t>2,57%</t>
-        </is>
-      </c>
-      <c r="V13" s="2" t="inlineStr">
-        <is>
-          <t>1,6%</t>
-        </is>
-      </c>
-      <c r="W13" s="2" t="inlineStr">
-        <is>
-          <t>3,49%</t>
         </is>
       </c>
     </row>
@@ -10807,102 +10807,102 @@
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>867433</t>
+          <t>679978</t>
         </is>
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>853215</t>
+          <t>668234</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>879999</t>
+          <t>687338</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
         <is>
+          <t>97,05%</t>
+        </is>
+      </c>
+      <c r="H14" s="2" t="inlineStr">
+        <is>
+          <t>95,38%</t>
+        </is>
+      </c>
+      <c r="I14" s="2" t="inlineStr">
+        <is>
+          <t>98,1%</t>
+        </is>
+      </c>
+      <c r="J14" s="2" t="inlineStr">
+        <is>
+          <t>1108</t>
+        </is>
+      </c>
+      <c r="K14" s="2" t="inlineStr">
+        <is>
+          <t>714747</t>
+        </is>
+      </c>
+      <c r="L14" s="2" t="inlineStr">
+        <is>
+          <t>705799</t>
+        </is>
+      </c>
+      <c r="M14" s="2" t="inlineStr">
+        <is>
+          <t>721177</t>
+        </is>
+      </c>
+      <c r="N14" s="2" t="inlineStr">
+        <is>
+          <t>97,0%</t>
+        </is>
+      </c>
+      <c r="O14" s="2" t="inlineStr">
+        <is>
+          <t>95,78%</t>
+        </is>
+      </c>
+      <c r="P14" s="2" t="inlineStr">
+        <is>
+          <t>97,87%</t>
+        </is>
+      </c>
+      <c r="Q14" s="2" t="inlineStr">
+        <is>
+          <t>1753</t>
+        </is>
+      </c>
+      <c r="R14" s="2" t="inlineStr">
+        <is>
+          <t>1394726</t>
+        </is>
+      </c>
+      <c r="S14" s="2" t="inlineStr">
+        <is>
+          <t>1381590</t>
+        </is>
+      </c>
+      <c r="T14" s="2" t="inlineStr">
+        <is>
+          <t>1404653</t>
+        </is>
+      </c>
+      <c r="U14" s="2" t="inlineStr">
+        <is>
+          <t>97,02%</t>
+        </is>
+      </c>
+      <c r="V14" s="2" t="inlineStr">
+        <is>
+          <t>96,11%</t>
+        </is>
+      </c>
+      <c r="W14" s="2" t="inlineStr">
+        <is>
           <t>97,71%</t>
-        </is>
-      </c>
-      <c r="H14" s="2" t="inlineStr">
-        <is>
-          <t>96,11%</t>
-        </is>
-      </c>
-      <c r="I14" s="2" t="inlineStr">
-        <is>
-          <t>99,12%</t>
-        </is>
-      </c>
-      <c r="J14" s="2" t="inlineStr">
-        <is>
-          <t>1108</t>
-        </is>
-      </c>
-      <c r="K14" s="2" t="inlineStr">
-        <is>
-          <t>692137</t>
-        </is>
-      </c>
-      <c r="L14" s="2" t="inlineStr">
-        <is>
-          <t>683873</t>
-        </is>
-      </c>
-      <c r="M14" s="2" t="inlineStr">
-        <is>
-          <t>698175</t>
-        </is>
-      </c>
-      <c r="N14" s="2" t="inlineStr">
-        <is>
-          <t>97,09%</t>
-        </is>
-      </c>
-      <c r="O14" s="2" t="inlineStr">
-        <is>
-          <t>95,93%</t>
-        </is>
-      </c>
-      <c r="P14" s="2" t="inlineStr">
-        <is>
-          <t>97,94%</t>
-        </is>
-      </c>
-      <c r="Q14" s="2" t="inlineStr">
-        <is>
-          <t>1753</t>
-        </is>
-      </c>
-      <c r="R14" s="2" t="inlineStr">
-        <is>
-          <t>1559570</t>
-        </is>
-      </c>
-      <c r="S14" s="2" t="inlineStr">
-        <is>
-          <t>1544751</t>
-        </is>
-      </c>
-      <c r="T14" s="2" t="inlineStr">
-        <is>
-          <t>1574977</t>
-        </is>
-      </c>
-      <c r="U14" s="2" t="inlineStr">
-        <is>
-          <t>97,43%</t>
-        </is>
-      </c>
-      <c r="V14" s="2" t="inlineStr">
-        <is>
-          <t>96,51%</t>
-        </is>
-      </c>
-      <c r="W14" s="2" t="inlineStr">
-        <is>
-          <t>98,4%</t>
         </is>
       </c>
     </row>
@@ -10920,17 +10920,17 @@
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>887786</t>
+          <t>700617</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>887786</t>
+          <t>700617</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>887786</t>
+          <t>700617</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
@@ -10955,17 +10955,17 @@
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>712881</t>
+          <t>736886</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>712881</t>
+          <t>736886</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>712881</t>
+          <t>736886</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -10990,17 +10990,17 @@
       </c>
       <c r="R15" s="2" t="inlineStr">
         <is>
-          <t>1600667</t>
+          <t>1437504</t>
         </is>
       </c>
       <c r="S15" s="2" t="inlineStr">
         <is>
-          <t>1600667</t>
+          <t>1437504</t>
         </is>
       </c>
       <c r="T15" s="2" t="inlineStr">
         <is>
-          <t>1600667</t>
+          <t>1437504</t>
         </is>
       </c>
       <c r="U15" s="2" t="inlineStr">
@@ -11037,32 +11037,32 @@
       </c>
       <c r="D16" s="2" t="inlineStr">
         <is>
-          <t>14961</t>
+          <t>15961</t>
         </is>
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>9068</t>
+          <t>9196</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>24146</t>
+          <t>25102</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
         <is>
-          <t>2,67%</t>
+          <t>2,62%</t>
         </is>
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>1,62%</t>
+          <t>1,51%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>4,3%</t>
+          <t>4,12%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -11072,27 +11072,27 @@
       </c>
       <c r="K16" s="2" t="inlineStr">
         <is>
-          <t>11602</t>
+          <t>13515</t>
         </is>
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>7020</t>
+          <t>8207</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>17892</t>
+          <t>19884</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
         <is>
-          <t>2,12%</t>
+          <t>2,22%</t>
         </is>
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>1,28%</t>
+          <t>1,35%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
@@ -11107,32 +11107,32 @@
       </c>
       <c r="R16" s="2" t="inlineStr">
         <is>
-          <t>26563</t>
+          <t>29476</t>
         </is>
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>18707</t>
+          <t>21168</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>37583</t>
+          <t>39637</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
         <is>
-          <t>2,39%</t>
+          <t>2,42%</t>
         </is>
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>1,69%</t>
+          <t>1,74%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>3,39%</t>
+          <t>3,25%</t>
         </is>
       </c>
     </row>
@@ -11150,32 +11150,32 @@
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>546273</t>
+          <t>593385</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>537088</t>
+          <t>584244</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>552166</t>
+          <t>600150</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>97,33%</t>
+          <t>97,38%</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>95,7%</t>
+          <t>95,88%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>98,38%</t>
+          <t>98,49%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -11185,22 +11185,22 @@
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>536303</t>
+          <t>595340</t>
         </is>
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>530013</t>
+          <t>588971</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>540885</t>
+          <t>600648</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>97,88%</t>
+          <t>97,78%</t>
         </is>
       </c>
       <c r="O17" s="2" t="inlineStr">
@@ -11210,7 +11210,7 @@
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>98,72%</t>
+          <t>98,65%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -11220,32 +11220,32 @@
       </c>
       <c r="R17" s="2" t="inlineStr">
         <is>
-          <t>1082576</t>
+          <t>1188726</t>
         </is>
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>1071556</t>
+          <t>1178565</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>1090432</t>
+          <t>1197034</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
         <is>
-          <t>97,61%</t>
+          <t>97,58%</t>
         </is>
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>96,61%</t>
+          <t>96,75%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>98,31%</t>
+          <t>98,26%</t>
         </is>
       </c>
     </row>
@@ -11263,17 +11263,17 @@
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>561234</t>
+          <t>609346</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>561234</t>
+          <t>609346</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>561234</t>
+          <t>609346</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -11298,17 +11298,17 @@
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>547905</t>
+          <t>608855</t>
         </is>
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>547905</t>
+          <t>608855</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>547905</t>
+          <t>608855</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -11333,17 +11333,17 @@
       </c>
       <c r="R18" s="2" t="inlineStr">
         <is>
-          <t>1109139</t>
+          <t>1218202</t>
         </is>
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>1109139</t>
+          <t>1218202</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>1109139</t>
+          <t>1218202</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -11380,32 +11380,32 @@
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>9774</t>
+          <t>11106</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>5558</t>
+          <t>6460</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>15889</t>
+          <t>17994</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>2,65%</t>
+          <t>2,73%</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>1,51%</t>
+          <t>1,59%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>4,32%</t>
+          <t>4,42%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -11415,32 +11415,32 @@
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>216866</t>
+          <t>14625</t>
         </is>
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>14868</t>
+          <t>9668</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>419562</t>
+          <t>22171</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
         <is>
-          <t>35,65%</t>
+          <t>3,33%</t>
         </is>
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>2,44%</t>
+          <t>2,2%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>68,97%</t>
+          <t>5,05%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -11450,32 +11450,32 @@
       </c>
       <c r="R19" s="2" t="inlineStr">
         <is>
-          <t>226640</t>
+          <t>25731</t>
         </is>
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>24538</t>
+          <t>18773</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>572784</t>
+          <t>35255</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
         <is>
-          <t>23,21%</t>
+          <t>3,04%</t>
         </is>
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>2,51%</t>
+          <t>2,22%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>58,65%</t>
+          <t>4,17%</t>
         </is>
       </c>
     </row>
@@ -11493,32 +11493,32 @@
       </c>
       <c r="D20" s="2" t="inlineStr">
         <is>
-          <t>358391</t>
+          <t>395974</t>
         </is>
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>352276</t>
+          <t>389086</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>362607</t>
+          <t>400620</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
         <is>
-          <t>97,35%</t>
+          <t>97,27%</t>
         </is>
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>95,68%</t>
+          <t>95,58%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>98,49%</t>
+          <t>98,41%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -11528,32 +11528,32 @@
       </c>
       <c r="K20" s="2" t="inlineStr">
         <is>
-          <t>391502</t>
+          <t>424541</t>
         </is>
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>188806</t>
+          <t>416995</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>593500</t>
+          <t>429498</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
         <is>
-          <t>64,35%</t>
+          <t>96,67%</t>
         </is>
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>31,03%</t>
+          <t>94,95%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>97,56%</t>
+          <t>97,8%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -11563,32 +11563,32 @@
       </c>
       <c r="R20" s="2" t="inlineStr">
         <is>
-          <t>749893</t>
+          <t>820515</t>
         </is>
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>403749</t>
+          <t>810991</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>951995</t>
+          <t>827473</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
         <is>
-          <t>76,79%</t>
+          <t>96,96%</t>
         </is>
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>41,35%</t>
+          <t>95,83%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>97,49%</t>
+          <t>97,78%</t>
         </is>
       </c>
     </row>
@@ -11606,17 +11606,17 @@
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>368165</t>
+          <t>407080</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>368165</t>
+          <t>407080</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>368165</t>
+          <t>407080</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
@@ -11641,17 +11641,17 @@
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>608368</t>
+          <t>439166</t>
         </is>
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>608368</t>
+          <t>439166</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>608368</t>
+          <t>439166</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
@@ -11676,17 +11676,17 @@
       </c>
       <c r="R21" s="2" t="inlineStr">
         <is>
-          <t>976533</t>
+          <t>846246</t>
         </is>
       </c>
       <c r="S21" s="2" t="inlineStr">
         <is>
-          <t>976533</t>
+          <t>846246</t>
         </is>
       </c>
       <c r="T21" s="2" t="inlineStr">
         <is>
-          <t>976533</t>
+          <t>846246</t>
         </is>
       </c>
       <c r="U21" s="2" t="inlineStr">
@@ -11723,32 +11723,32 @@
       </c>
       <c r="D22" s="2" t="inlineStr">
         <is>
-          <t>9055</t>
+          <t>9619</t>
         </is>
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>5058</t>
+          <t>5359</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>15083</t>
+          <t>16170</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
         <is>
-          <t>3,2%</t>
+          <t>3,1%</t>
         </is>
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>1,79%</t>
+          <t>1,73%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>5,33%</t>
+          <t>5,21%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -11758,32 +11758,32 @@
       </c>
       <c r="K22" s="2" t="inlineStr">
         <is>
-          <t>19869</t>
+          <t>21569</t>
         </is>
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>14888</t>
+          <t>15393</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>27231</t>
+          <t>29165</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
         <is>
-          <t>4,67%</t>
+          <t>4,64%</t>
         </is>
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>3,5%</t>
+          <t>3,31%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>6,39%</t>
+          <t>6,28%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -11793,32 +11793,32 @@
       </c>
       <c r="R22" s="2" t="inlineStr">
         <is>
-          <t>28924</t>
+          <t>31188</t>
         </is>
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>21592</t>
+          <t>23458</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>37402</t>
+          <t>40585</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
         <is>
-          <t>4,08%</t>
+          <t>4,03%</t>
         </is>
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>3,05%</t>
+          <t>3,03%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>5,28%</t>
+          <t>5,24%</t>
         </is>
       </c>
     </row>
@@ -11836,32 +11836,32 @@
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>273704</t>
+          <t>300579</t>
         </is>
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>267676</t>
+          <t>294028</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>277701</t>
+          <t>304839</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
         <is>
-          <t>96,8%</t>
+          <t>96,9%</t>
         </is>
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>94,67%</t>
+          <t>94,79%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>98,21%</t>
+          <t>98,27%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -11871,32 +11871,32 @@
       </c>
       <c r="K23" s="2" t="inlineStr">
         <is>
-          <t>405962</t>
+          <t>443040</t>
         </is>
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>398600</t>
+          <t>435444</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>410943</t>
+          <t>449216</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
         <is>
-          <t>95,33%</t>
+          <t>95,36%</t>
         </is>
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>93,61%</t>
+          <t>93,72%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>96,5%</t>
+          <t>96,69%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -11906,32 +11906,32 @@
       </c>
       <c r="R23" s="2" t="inlineStr">
         <is>
-          <t>679666</t>
+          <t>743619</t>
         </is>
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>671188</t>
+          <t>734222</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>686998</t>
+          <t>751349</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
         <is>
-          <t>95,92%</t>
+          <t>95,97%</t>
         </is>
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>94,72%</t>
+          <t>94,76%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>96,95%</t>
+          <t>96,97%</t>
         </is>
       </c>
     </row>
@@ -11949,17 +11949,17 @@
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>282759</t>
+          <t>310198</t>
         </is>
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>282759</t>
+          <t>310198</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>282759</t>
+          <t>310198</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
@@ -11984,17 +11984,17 @@
       </c>
       <c r="K24" s="2" t="inlineStr">
         <is>
-          <t>425831</t>
+          <t>464609</t>
         </is>
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>425831</t>
+          <t>464609</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>425831</t>
+          <t>464609</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
@@ -12019,17 +12019,17 @@
       </c>
       <c r="R24" s="2" t="inlineStr">
         <is>
-          <t>708590</t>
+          <t>774807</t>
         </is>
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>708590</t>
+          <t>774807</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>708590</t>
+          <t>774807</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
@@ -12066,32 +12066,32 @@
       </c>
       <c r="D25" s="2" t="inlineStr">
         <is>
-          <t>72985</t>
+          <t>81098</t>
         </is>
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>53415</t>
+          <t>64472</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>92622</t>
+          <t>102248</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
         <is>
-          <t>2,11%</t>
+          <t>2,3%</t>
         </is>
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>1,54%</t>
+          <t>1,82%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>2,68%</t>
+          <t>2,89%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -12101,67 +12101,67 @@
       </c>
       <c r="K25" s="2" t="inlineStr">
         <is>
-          <t>304229</t>
+          <t>114160</t>
         </is>
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>99799</t>
+          <t>97053</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>932453</t>
+          <t>135221</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
         <is>
-          <t>8,2%</t>
+          <t>3,05%</t>
         </is>
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
+          <t>2,6%</t>
+        </is>
+      </c>
+      <c r="P25" s="2" t="inlineStr">
+        <is>
+          <t>3,62%</t>
+        </is>
+      </c>
+      <c r="Q25" s="2" t="inlineStr">
+        <is>
+          <t>242</t>
+        </is>
+      </c>
+      <c r="R25" s="2" t="inlineStr">
+        <is>
+          <t>195258</t>
+        </is>
+      </c>
+      <c r="S25" s="2" t="inlineStr">
+        <is>
+          <t>170301</t>
+        </is>
+      </c>
+      <c r="T25" s="2" t="inlineStr">
+        <is>
+          <t>223138</t>
+        </is>
+      </c>
+      <c r="U25" s="2" t="inlineStr">
+        <is>
           <t>2,69%</t>
         </is>
       </c>
-      <c r="P25" s="2" t="inlineStr">
-        <is>
-          <t>25,12%</t>
-        </is>
-      </c>
-      <c r="Q25" s="2" t="inlineStr">
-        <is>
-          <t>242</t>
-        </is>
-      </c>
-      <c r="R25" s="2" t="inlineStr">
-        <is>
-          <t>377213</t>
-        </is>
-      </c>
-      <c r="S25" s="2" t="inlineStr">
-        <is>
-          <t>168822</t>
-        </is>
-      </c>
-      <c r="T25" s="2" t="inlineStr">
-        <is>
-          <t>1039504</t>
-        </is>
-      </c>
-      <c r="U25" s="2" t="inlineStr">
-        <is>
-          <t>5,26%</t>
-        </is>
-      </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>2,35%</t>
+          <t>2,34%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>14,49%</t>
+          <t>3,07%</t>
         </is>
       </c>
     </row>
@@ -12179,32 +12179,32 @@
       </c>
       <c r="D26" s="2" t="inlineStr">
         <is>
-          <t>3386832</t>
+          <t>3451664</t>
         </is>
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>3367195</t>
+          <t>3430514</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>3406402</t>
+          <t>3468290</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
         <is>
-          <t>97,89%</t>
+          <t>97,7%</t>
         </is>
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>97,32%</t>
+          <t>97,11%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>98,46%</t>
+          <t>98,18%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -12214,67 +12214,67 @@
       </c>
       <c r="K26" s="2" t="inlineStr">
         <is>
-          <t>3408051</t>
+          <t>3622794</t>
         </is>
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>2779827</t>
+          <t>3601733</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>3612481</t>
+          <t>3639901</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
         <is>
-          <t>91,8%</t>
+          <t>96,95%</t>
         </is>
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>74,88%</t>
+          <t>96,38%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
+          <t>97,4%</t>
+        </is>
+      </c>
+      <c r="Q26" s="2" t="inlineStr">
+        <is>
+          <t>8501</t>
+        </is>
+      </c>
+      <c r="R26" s="2" t="inlineStr">
+        <is>
+          <t>7074458</t>
+        </is>
+      </c>
+      <c r="S26" s="2" t="inlineStr">
+        <is>
+          <t>7046578</t>
+        </is>
+      </c>
+      <c r="T26" s="2" t="inlineStr">
+        <is>
+          <t>7099415</t>
+        </is>
+      </c>
+      <c r="U26" s="2" t="inlineStr">
+        <is>
           <t>97,31%</t>
         </is>
       </c>
-      <c r="Q26" s="2" t="inlineStr">
-        <is>
-          <t>8501</t>
-        </is>
-      </c>
-      <c r="R26" s="2" t="inlineStr">
-        <is>
-          <t>6794884</t>
-        </is>
-      </c>
-      <c r="S26" s="2" t="inlineStr">
-        <is>
-          <t>6132593</t>
-        </is>
-      </c>
-      <c r="T26" s="2" t="inlineStr">
-        <is>
-          <t>7003275</t>
-        </is>
-      </c>
-      <c r="U26" s="2" t="inlineStr">
-        <is>
-          <t>94,74%</t>
-        </is>
-      </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>85,51%</t>
+          <t>96,93%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>97,65%</t>
+          <t>97,66%</t>
         </is>
       </c>
     </row>
@@ -12292,17 +12292,17 @@
       </c>
       <c r="D27" s="2" t="inlineStr">
         <is>
-          <t>3459817</t>
+          <t>3532762</t>
         </is>
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>3459817</t>
+          <t>3532762</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>3459817</t>
+          <t>3532762</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
@@ -12327,17 +12327,17 @@
       </c>
       <c r="K27" s="2" t="inlineStr">
         <is>
-          <t>3712280</t>
+          <t>3736954</t>
         </is>
       </c>
       <c r="L27" s="2" t="inlineStr">
         <is>
-          <t>3712280</t>
+          <t>3736954</t>
         </is>
       </c>
       <c r="M27" s="2" t="inlineStr">
         <is>
-          <t>3712280</t>
+          <t>3736954</t>
         </is>
       </c>
       <c r="N27" s="2" t="inlineStr">
@@ -12362,17 +12362,17 @@
       </c>
       <c r="R27" s="2" t="inlineStr">
         <is>
-          <t>7172097</t>
+          <t>7269716</t>
         </is>
       </c>
       <c r="S27" s="2" t="inlineStr">
         <is>
-          <t>7172097</t>
+          <t>7269716</t>
         </is>
       </c>
       <c r="T27" s="2" t="inlineStr">
         <is>
-          <t>7172097</t>
+          <t>7269716</t>
         </is>
       </c>
       <c r="U27" s="2" t="inlineStr">

--- a/data/trans_orig/P2A_psíq_R-Edad-trans_orig.xlsx
+++ b/data/trans_orig/P2A_psíq_R-Edad-trans_orig.xlsx
@@ -538,7 +538,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Hogares según si tienen personas con limitación por discapacidad psíquica en 2007 (tasa de respuesta: 100,0%)</t>
+          <t>Población según si convive con personas con alguna limitación por discapacidad psíquica en 2007 (tasa de respuesta: 100,0%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -3517,7 +3517,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Hogares según si tienen personas con limitación por discapacidad psíquica en 2012 (tasa de respuesta: 100,0%)</t>
+          <t>Población según si convive con personas con alguna limitación por discapacidad psíquica en 2012 (tasa de respuesta: 100,0%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -6496,7 +6496,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Hogares según si tienen personas con limitación por discapacidad psíquica en 2016 (tasa de respuesta: 100,0%)</t>
+          <t>Población según si convive con personas con alguna limitación por discapacidad psíquica en 2016 (tasa de respuesta: 100,0%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -9475,7 +9475,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Hogares según si tienen personas con limitación por discapacidad psíquica en 2023 (tasa de respuesta: 100,0%)</t>
+          <t>Población según si convive con personas con alguna limitación por discapacidad psíquica en 2023 (tasa de respuesta: 100,0%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
